--- a/files/九龙-启德-维港．湾畔第1B期.xlsx
+++ b/files/九龙-启德-维港．湾畔第1B期.xlsx
@@ -8,8 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2A座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2B座 销控表" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -112,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -177,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -193,51 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -25535,4815 +25395,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:J34"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>维港．湾畔第1B期 - 2A座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>261 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>3 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>69 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>189 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 557呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>B | 565呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>C | 450呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E6" s="17" t="inlineStr">
-        <is>
-          <t>D | 300呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F6" s="17" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G6" s="17" t="inlineStr">
-        <is>
-          <t>F | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H6" s="17" t="inlineStr">
-        <is>
-          <t>G | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I6" s="17" t="inlineStr">
-        <is>
-          <t>H | 309呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J6" s="17" t="inlineStr">
-        <is>
-          <t>J | 559呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>A | 560呎 (2房)
-$1,921万
-$34,307/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>B | 516呎 (2房)
-$1,742万
-$33,756/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>C | 450呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>D | 300呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F7" s="17" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G7" s="17" t="inlineStr">
-        <is>
-          <t>F | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H7" s="17" t="inlineStr">
-        <is>
-          <t>G | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I7" s="17" t="inlineStr">
-        <is>
-          <t>H | 309呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J7" s="17" t="inlineStr">
-        <is>
-          <t>J | 559呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 560呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>B | 516呎 (2房)
-$1,692万
-$32,791/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>C | 450呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E8" s="17" t="inlineStr">
-        <is>
-          <t>D | 300呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F8" s="17" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G8" s="17" t="inlineStr">
-        <is>
-          <t>F | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H8" s="17" t="inlineStr">
-        <is>
-          <t>G | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I8" s="17" t="inlineStr">
-        <is>
-          <t>H | 309呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J8" s="17" t="inlineStr">
-        <is>
-          <t>J | 559呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>A | 560呎 (2房)
-$1,848万
-$32,993/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>B | 516呎 (2房)
-$1,675万
-$32,467/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>C | 450呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E9" s="17" t="inlineStr">
-        <is>
-          <t>D | 300呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F9" s="17" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G9" s="17" t="inlineStr">
-        <is>
-          <t>F | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H9" s="17" t="inlineStr">
-        <is>
-          <t>G | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I9" s="17" t="inlineStr">
-        <is>
-          <t>H | 309呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J9" s="17" t="inlineStr">
-        <is>
-          <t>J | 559呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>A | 560呎 (2房)
-$1,794万
-$32,030/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>B | 516呎 (2房)
-$1,627万
-$31,527/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>C | 450呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E10" s="17" t="inlineStr">
-        <is>
-          <t>D | 300呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F10" s="17" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G10" s="17" t="inlineStr">
-        <is>
-          <t>F | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H10" s="17" t="inlineStr">
-        <is>
-          <t>G | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I10" s="17" t="inlineStr">
-        <is>
-          <t>H | 309呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J10" s="17" t="inlineStr">
-        <is>
-          <t>J | 559呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>A | 560呎 (2房)
-$1,776万
-$31,714/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>B | 516呎 (2房)
-$1,611万
-$31,215/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t>C | 450呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E11" s="17" t="inlineStr">
-        <is>
-          <t>D | 300呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F11" s="17" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G11" s="17" t="inlineStr">
-        <is>
-          <t>F | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H11" s="17" t="inlineStr">
-        <is>
-          <t>G | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I11" s="17" t="inlineStr">
-        <is>
-          <t>H | 309呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J11" s="17" t="inlineStr">
-        <is>
-          <t>J | 559呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>A | 560呎 (2房)
-$1,758万
-$31,400/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>B | 516呎 (2房)
-$1,595万
-$30,907/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t>C | 450呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E12" s="17" t="inlineStr">
-        <is>
-          <t>D | 300呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F12" s="17" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G12" s="17" t="inlineStr">
-        <is>
-          <t>F | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H12" s="17" t="inlineStr">
-        <is>
-          <t>G | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I12" s="17" t="inlineStr">
-        <is>
-          <t>H | 309呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J12" s="17" t="inlineStr">
-        <is>
-          <t>J | 559呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>A | 560呎 (2房)
-$1,743万
-$31,130/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>B | 516呎 (2房)
-$1,548万
-$30,000/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>C | 450呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E13" s="17" t="inlineStr">
-        <is>
-          <t>D | 300呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F13" s="17" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G13" s="17" t="inlineStr">
-        <is>
-          <t>F | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H13" s="17" t="inlineStr">
-        <is>
-          <t>G | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I13" s="17" t="inlineStr">
-        <is>
-          <t>H | 309呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J13" s="17" t="inlineStr">
-        <is>
-          <t>J | 559呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>A | 560呎 (2房)
-$1,715万
-$30,627/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>B | 516呎 (2房)
-$1,540万
-$29,851/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>C | 450呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E14" s="17" t="inlineStr">
-        <is>
-          <t>D | 300呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F14" s="17" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G14" s="17" t="inlineStr">
-        <is>
-          <t>F | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H14" s="17" t="inlineStr">
-        <is>
-          <t>G | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I14" s="17" t="inlineStr">
-        <is>
-          <t>H | 309呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J14" s="17" t="inlineStr">
-        <is>
-          <t>J | 559呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>A | 560呎 (2房)
-$1,707万
-$30,475/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>B | 516呎 (2房)
-$1,533万
-$29,702/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D15" s="17" t="inlineStr">
-        <is>
-          <t>C | 450呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E15" s="17" t="inlineStr">
-        <is>
-          <t>D | 300呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F15" s="17" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G15" s="17" t="inlineStr">
-        <is>
-          <t>F | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H15" s="17" t="inlineStr">
-        <is>
-          <t>G | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I15" s="17" t="inlineStr">
-        <is>
-          <t>H | 309呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J15" s="17" t="inlineStr">
-        <is>
-          <t>J | 559呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>A | 560呎 (2房)
-$1,715万
-$30,627/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>B | 516呎 (2房)
-$1,525万
-$29,554/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D16" s="17" t="inlineStr">
-        <is>
-          <t>C | 450呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E16" s="17" t="inlineStr">
-        <is>
-          <t>D | 300呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F16" s="17" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G16" s="17" t="inlineStr">
-        <is>
-          <t>F | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H16" s="17" t="inlineStr">
-        <is>
-          <t>G | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I16" s="17" t="inlineStr">
-        <is>
-          <t>H | 309呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J16" s="17" t="inlineStr">
-        <is>
-          <t>J | 559呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>A | 560呎 (2房)
-$1,707万
-$30,475/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>B | 516呎 (2房)
-$1,517万
-$29,407/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>C | 450呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E17" s="17" t="inlineStr">
-        <is>
-          <t>D | 300呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F17" s="17" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G17" s="17" t="inlineStr">
-        <is>
-          <t>F | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H17" s="17" t="inlineStr">
-        <is>
-          <t>G | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I17" s="17" t="inlineStr">
-        <is>
-          <t>H | 309呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J17" s="16" t="inlineStr">
-        <is>
-          <t>J | 559呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>A | 560呎 (2房)
-$1,681万
-$30,023/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>B | 516呎 (2房)
-$1,510万
-$29,260/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t>C | 450呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E18" s="17" t="inlineStr">
-        <is>
-          <t>D | 300呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F18" s="17" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G18" s="17" t="inlineStr">
-        <is>
-          <t>F | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H18" s="17" t="inlineStr">
-        <is>
-          <t>G | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I18" s="17" t="inlineStr">
-        <is>
-          <t>H | 309呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J18" s="18" t="inlineStr">
-        <is>
-          <t>J | 559呎 (2房)
-$1,832万
-$32,771/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>A | 560呎 (2房)
-$1,673万
-$29,873/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>B | 516呎 (2房)
-$1,502万
-$29,114/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
-        <is>
-          <t>C | 450呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E19" s="17" t="inlineStr">
-        <is>
-          <t>D | 300呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F19" s="17" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G19" s="17" t="inlineStr">
-        <is>
-          <t>F | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H19" s="17" t="inlineStr">
-        <is>
-          <t>G | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I19" s="17" t="inlineStr">
-        <is>
-          <t>H | 309呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J19" s="18" t="inlineStr">
-        <is>
-          <t>J | 559呎 (2房)
-$1,823万
-$32,610/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>A | 560呎 (2房)
-$1,664万
-$29,723/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>B | 516呎 (2房)
-$1,495万
-$28,969/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
-        <is>
-          <t>C | 450呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E20" s="17" t="inlineStr">
-        <is>
-          <t>D | 300呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F20" s="17" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G20" s="17" t="inlineStr">
-        <is>
-          <t>F | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H20" s="17" t="inlineStr">
-        <is>
-          <t>G | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I20" s="17" t="inlineStr">
-        <is>
-          <t>H | 309呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J20" s="18" t="inlineStr">
-        <is>
-          <t>J | 559呎 (2房)
-$1,780万
-$31,844/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>A | 560呎 (2房)
-$1,694万
-$30,246/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>B | 516呎 (2房)
-$1,487万
-$28,826/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D21" s="17" t="inlineStr">
-        <is>
-          <t>C | 450呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E21" s="17" t="inlineStr">
-        <is>
-          <t>D | 300呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F21" s="17" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G21" s="17" t="inlineStr">
-        <is>
-          <t>F | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H21" s="17" t="inlineStr">
-        <is>
-          <t>G | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I21" s="17" t="inlineStr">
-        <is>
-          <t>H | 309呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J21" s="18" t="inlineStr">
-        <is>
-          <t>J | 559呎 (2房)
-$1,805万
-$32,283/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>A | 560呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>B | 516呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="inlineStr">
-        <is>
-          <t>C | 450呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E22" s="17" t="inlineStr">
-        <is>
-          <t>D | 300呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F22" s="17" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G22" s="17" t="inlineStr">
-        <is>
-          <t>F | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H22" s="17" t="inlineStr">
-        <is>
-          <t>G | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I22" s="17" t="inlineStr">
-        <is>
-          <t>H | 309呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J22" s="17" t="inlineStr">
-        <is>
-          <t>J | 559呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>A | 560呎 (2房)
-$1,631万
-$29,132/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>B | 516呎 (2房)
-$1,465万
-$28,393/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D23" s="17" t="inlineStr">
-        <is>
-          <t>C | 450呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E23" s="17" t="inlineStr">
-        <is>
-          <t>D | 300呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F23" s="17" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G23" s="17" t="inlineStr">
-        <is>
-          <t>F | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H23" s="17" t="inlineStr">
-        <is>
-          <t>G | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I23" s="17" t="inlineStr">
-        <is>
-          <t>H | 309呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J23" s="18" t="inlineStr">
-        <is>
-          <t>J | 559呎 (2房)
-$1,734万
-$31,018/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>A | 560呎 (2房)
-$1,623万
-$28,988/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="inlineStr">
-        <is>
-          <t>B | 516呎 (2房)
-$1,458万
-$28,252/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D24" s="17" t="inlineStr">
-        <is>
-          <t>C | 450呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E24" s="17" t="inlineStr">
-        <is>
-          <t>D | 300呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F24" s="17" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G24" s="17" t="inlineStr">
-        <is>
-          <t>F | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H24" s="17" t="inlineStr">
-        <is>
-          <t>G | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I24" s="17" t="inlineStr">
-        <is>
-          <t>H | 309呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J24" s="18" t="inlineStr">
-        <is>
-          <t>J | 559呎 (2房)
-$1,759万
-$31,460/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="inlineStr">
-        <is>
-          <t>A | 560呎 (2房)
-$1,615万
-$28,843/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>B | 516呎 (2房)
-$1,450万
-$28,110/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D25" s="17" t="inlineStr">
-        <is>
-          <t>C | 450呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E25" s="17" t="inlineStr">
-        <is>
-          <t>D | 300呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F25" s="17" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G25" s="17" t="inlineStr">
-        <is>
-          <t>F | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H25" s="17" t="inlineStr">
-        <is>
-          <t>G | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I25" s="17" t="inlineStr">
-        <is>
-          <t>H | 309呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J25" s="18" t="inlineStr">
-        <is>
-          <t>J | 559呎 (2房)
-$1,711万
-$30,608/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B26" s="18" t="inlineStr">
-        <is>
-          <t>A | 560呎 (2房)
-$1,607万
-$28,698/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="inlineStr">
-        <is>
-          <t>B | 516呎 (2房)
-$1,443万
-$27,969/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D26" s="17" t="inlineStr">
-        <is>
-          <t>C | 450呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E26" s="17" t="inlineStr">
-        <is>
-          <t>D | 300呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F26" s="17" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G26" s="17" t="inlineStr">
-        <is>
-          <t>F | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H26" s="17" t="inlineStr">
-        <is>
-          <t>G | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I26" s="17" t="inlineStr">
-        <is>
-          <t>H | 309呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J26" s="18" t="inlineStr">
-        <is>
-          <t>J | 559呎 (2房)
-$1,758万
-$31,444/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B27" s="18" t="inlineStr">
-        <is>
-          <t>A | 560呎 (2房)
-$1,599万
-$28,555/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C27" s="18" t="inlineStr">
-        <is>
-          <t>B | 516呎 (2房)
-$1,436万
-$27,829/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D27" s="17" t="inlineStr">
-        <is>
-          <t>C | 450呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E27" s="17" t="inlineStr">
-        <is>
-          <t>D | 300呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F27" s="17" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G27" s="17" t="inlineStr">
-        <is>
-          <t>F | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H27" s="17" t="inlineStr">
-        <is>
-          <t>G | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I27" s="17" t="inlineStr">
-        <is>
-          <t>H | 309呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J27" s="18" t="inlineStr">
-        <is>
-          <t>J | 559呎 (2房)
-$1,710万
-$30,592/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B28" s="18" t="inlineStr">
-        <is>
-          <t>A | 560呎 (2房)
-$1,591万
-$28,412/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C28" s="18" t="inlineStr">
-        <is>
-          <t>B | 516呎 (2房)
-$1,429万
-$27,692/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D28" s="17" t="inlineStr">
-        <is>
-          <t>C | 450呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E28" s="17" t="inlineStr">
-        <is>
-          <t>D | 300呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F28" s="17" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G28" s="17" t="inlineStr">
-        <is>
-          <t>F | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H28" s="17" t="inlineStr">
-        <is>
-          <t>G | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I28" s="17" t="inlineStr">
-        <is>
-          <t>H | 309呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J28" s="18" t="inlineStr">
-        <is>
-          <t>J | 559呎 (2房)
-$1,702万
-$30,440/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B29" s="18" t="inlineStr">
-        <is>
-          <t>A | 560呎 (2房)
-$1,583万
-$28,270/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C29" s="18" t="inlineStr">
-        <is>
-          <t>B | 516呎 (2房)
-$1,422万
-$27,552/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="D29" s="17" t="inlineStr">
-        <is>
-          <t>C | 450呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E29" s="17" t="inlineStr">
-        <is>
-          <t>D | 300呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F29" s="17" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G29" s="17" t="inlineStr">
-        <is>
-          <t>F | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H29" s="17" t="inlineStr">
-        <is>
-          <t>G | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I29" s="17" t="inlineStr">
-        <is>
-          <t>H | 309呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J29" s="18" t="inlineStr">
-        <is>
-          <t>J | 559呎 (2房)
-$1,693万
-$30,288/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B30" s="18" t="inlineStr">
-        <is>
-          <t>A | 560呎 (2房)
-$1,559万
-$27,846/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C30" s="18" t="inlineStr">
-        <is>
-          <t>B | 516呎 (2房)
-$1,400万
-$27,140/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D30" s="17" t="inlineStr">
-        <is>
-          <t>C | 450呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E30" s="17" t="inlineStr">
-        <is>
-          <t>D | 300呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F30" s="17" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G30" s="17" t="inlineStr">
-        <is>
-          <t>F | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H30" s="17" t="inlineStr">
-        <is>
-          <t>G | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I30" s="17" t="inlineStr">
-        <is>
-          <t>H | 309呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J30" s="18" t="inlineStr">
-        <is>
-          <t>J | 559呎 (2房)
-$1,652万
-$29,551/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B31" s="18" t="inlineStr">
-        <is>
-          <t>A | 560呎 (2房)
-$1,579万
-$28,195/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C31" s="18" t="inlineStr">
-        <is>
-          <t>B | 516呎 (2房)
-$1,386万
-$26,868/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D31" s="17" t="inlineStr">
-        <is>
-          <t>C | 450呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E31" s="17" t="inlineStr">
-        <is>
-          <t>D | 300呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F31" s="17" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G31" s="17" t="inlineStr">
-        <is>
-          <t>F | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H31" s="17" t="inlineStr">
-        <is>
-          <t>G | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I31" s="17" t="inlineStr">
-        <is>
-          <t>H | 309呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J31" s="18" t="inlineStr">
-        <is>
-          <t>J | 559呎 (2房)
-$1,620万
-$28,977/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B32" s="18" t="inlineStr">
-        <is>
-          <t>A | 560呎 (2房)
-$1,528万
-$27,291/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="C32" s="18" t="inlineStr">
-        <is>
-          <t>B | 516呎 (2房)
-$1,372万
-$26,599/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D32" s="17" t="inlineStr">
-        <is>
-          <t>C | 450呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E32" s="17" t="inlineStr">
-        <is>
-          <t>D | 300呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F32" s="17" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G32" s="17" t="inlineStr">
-        <is>
-          <t>F | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H32" s="17" t="inlineStr">
-        <is>
-          <t>G | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I32" s="17" t="inlineStr">
-        <is>
-          <t>H | 309呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J32" s="18" t="inlineStr">
-        <is>
-          <t>J | 559呎 (2房)
-$1,619万
-$28,962/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B33" s="18" t="inlineStr">
-        <is>
-          <t>A | 560呎 (2房)
-$1,540万
-$27,493/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C33" s="18" t="inlineStr">
-        <is>
-          <t>B | 516呎 (2房)
-$1,352万
-$26,200/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D33" s="17" t="inlineStr">
-        <is>
-          <t>C | 450呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E33" s="17" t="inlineStr">
-        <is>
-          <t>D | 300呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F33" s="17" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G33" s="17" t="inlineStr">
-        <is>
-          <t>F | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H33" s="17" t="inlineStr">
-        <is>
-          <t>G | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I33" s="17" t="inlineStr">
-        <is>
-          <t>H | 309呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J33" s="18" t="inlineStr">
-        <is>
-          <t>J | 559呎 (2房)
-$1,580万
-$28,258/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B34" s="18" t="inlineStr">
-        <is>
-          <t>A | 560呎 (2房)
-$1,483万
-$26,488/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C34" s="18" t="inlineStr">
-        <is>
-          <t>B | 516呎 (2房)
-$1,333万
-$25,828/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="D34" s="17" t="inlineStr">
-        <is>
-          <t>C | 450呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E34" s="17" t="inlineStr">
-        <is>
-          <t>D | 300呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F34" s="17" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G34" s="17" t="inlineStr">
-        <is>
-          <t>F | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H34" s="17" t="inlineStr">
-        <is>
-          <t>G | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I34" s="17" t="inlineStr">
-        <is>
-          <t>H | 309呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J34" s="18" t="inlineStr">
-        <is>
-          <t>J | 559呎 (2房)
-$1,586万
-$28,369/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:J34"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>维港．湾畔第1B期 - 2B座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>250 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>4 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>102 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>143 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>A | 670呎 (3房)
-$2,424万
-$36,187/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>B | 592呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>C | 568呎 (3房)
-$2,117万
-$37,276/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E6" s="17" t="inlineStr">
-        <is>
-          <t>D | 498呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F6" s="17" t="inlineStr">
-        <is>
-          <t>E | 456呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G6" s="17" t="inlineStr">
-        <is>
-          <t>F | 452呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H6" s="17" t="inlineStr">
-        <is>
-          <t>G | 457呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I6" s="17" t="inlineStr">
-        <is>
-          <t>H | 466呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J6" s="19" t="inlineStr">
-        <is>
-          <t>J | 549呎 (2房)
-$2,126万
-$38,727/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>A | 670呎 (3房)
-$2,320万
-$34,634/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>B | 579呎 (2房)
-$2,047万
-$35,361/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>C | 568呎 (3房)
-$1,993万
-$35,086/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>D | 498呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F7" s="17" t="inlineStr">
-        <is>
-          <t>E | 456呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G7" s="17" t="inlineStr">
-        <is>
-          <t>F | 452呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H7" s="17" t="inlineStr">
-        <is>
-          <t>G | 457呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I7" s="17" t="inlineStr">
-        <is>
-          <t>H | 466呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J7" s="19" t="inlineStr">
-        <is>
-          <t>J | 549呎 (2房)
-$2,095万
-$38,153/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>A | 670呎 (3房)
-$2,298万
-$34,291/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>B | 579呎 (2房)
-$1,956万
-$33,777/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>C | 568呎 (3房)
-$2,050万
-$36,088/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E8" s="17" t="inlineStr">
-        <is>
-          <t>D | 498呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F8" s="17" t="inlineStr">
-        <is>
-          <t>E | 456呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G8" s="17" t="inlineStr">
-        <is>
-          <t>F | 452呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H8" s="17" t="inlineStr">
-        <is>
-          <t>G | 457呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I8" s="17" t="inlineStr">
-        <is>
-          <t>H | 466呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J8" s="18" t="inlineStr">
-        <is>
-          <t>J | 549呎 (2房)
-$1,825万
-$33,242/呎
-(26年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>A | 670呎 (3房)
-$2,275万
-$33,952/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>B | 579呎 (2房)
-$1,931万
-$33,356/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>C | 568呎 (3房)
-$2,086万
-$36,732/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="E9" s="17" t="inlineStr">
-        <is>
-          <t>D | 498呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F9" s="17" t="inlineStr">
-        <is>
-          <t>E | 456呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G9" s="17" t="inlineStr">
-        <is>
-          <t>F | 452呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H9" s="17" t="inlineStr">
-        <is>
-          <t>G | 457呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I9" s="17" t="inlineStr">
-        <is>
-          <t>H | 466呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J9" s="16" t="inlineStr">
-        <is>
-          <t>J | 549呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>A | 670呎 (3房)
-$2,252万
-$33,613/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>B | 579呎 (2房)
-$1,912万
-$33,026/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>C | 568呎 (3房)
-$1,972万
-$34,715/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E10" s="17" t="inlineStr">
-        <is>
-          <t>D | 498呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F10" s="17" t="inlineStr">
-        <is>
-          <t>E | 456呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G10" s="17" t="inlineStr">
-        <is>
-          <t>F | 452呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H10" s="17" t="inlineStr">
-        <is>
-          <t>G | 457呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I10" s="17" t="inlineStr">
-        <is>
-          <t>H | 466呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J10" s="18" t="inlineStr">
-        <is>
-          <t>J | 549呎 (2房)
-$1,878万
-$34,217/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>A | 670呎 (3房)
-$2,230万
-$33,282/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>B | 579呎 (2房)
-$1,968万
-$33,981/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>C | 568呎 (3房)
-$1,952万
-$34,371/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E11" s="17" t="inlineStr">
-        <is>
-          <t>D | 498呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F11" s="17" t="inlineStr">
-        <is>
-          <t>E | 456呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G11" s="17" t="inlineStr">
-        <is>
-          <t>F | 452呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H11" s="17" t="inlineStr">
-        <is>
-          <t>G | 457呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I11" s="17" t="inlineStr">
-        <is>
-          <t>H | 466呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J11" s="19" t="inlineStr">
-        <is>
-          <t>J | 549呎 (2房)
-$2,013万
-$36,665/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>A | 670呎 (3房)
-$2,186万
-$32,630/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>B | 579呎 (2房)
-$1,948万
-$33,644/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>C | 568呎 (3房)
-$1,915万
-$33,708/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E12" s="17" t="inlineStr">
-        <is>
-          <t>D | 498呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F12" s="17" t="inlineStr">
-        <is>
-          <t>E | 456呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G12" s="17" t="inlineStr">
-        <is>
-          <t>F | 452呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H12" s="17" t="inlineStr">
-        <is>
-          <t>G | 457呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I12" s="17" t="inlineStr">
-        <is>
-          <t>H | 466呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J12" s="18" t="inlineStr">
-        <is>
-          <t>J | 549呎 (2房)
-$1,789万
-$32,583/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>A | 669呎 (3房)
-$2,143万
-$32,033/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>B | 579呎 (2房)
-$1,856万
-$32,054/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>C | 568呎 (3房)
-$1,859万
-$32,732/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E13" s="17" t="inlineStr">
-        <is>
-          <t>D | 498呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F13" s="17" t="inlineStr">
-        <is>
-          <t>E | 456呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G13" s="17" t="inlineStr">
-        <is>
-          <t>F | 452呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H13" s="17" t="inlineStr">
-        <is>
-          <t>G | 457呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I13" s="17" t="inlineStr">
-        <is>
-          <t>H | 466呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J13" s="18" t="inlineStr">
-        <is>
-          <t>J | 549呎 (2房)
-$1,791万
-$32,630/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>A | 669呎 (3房)
-$2,132万
-$31,874/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>B | 579呎 (2房)
-$1,831万
-$31,623/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>C | 568呎 (3房)
-$1,814万
-$31,930/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E14" s="17" t="inlineStr">
-        <is>
-          <t>D | 498呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F14" s="17" t="inlineStr">
-        <is>
-          <t>E | 456呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G14" s="17" t="inlineStr">
-        <is>
-          <t>F | 452呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H14" s="17" t="inlineStr">
-        <is>
-          <t>G | 457呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I14" s="17" t="inlineStr">
-        <is>
-          <t>H | 466呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J14" s="19" t="inlineStr">
-        <is>
-          <t>J | 549呎 (2房)
-$1,963万
-$35,761/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>A | 669呎 (3房)
-$2,192万
-$32,762/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>B | 579呎 (2房)
-$1,802万
-$31,114/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>C | 568呎 (3房)
-$1,841万
-$32,407/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E15" s="17" t="inlineStr">
-        <is>
-          <t>D | 498呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F15" s="17" t="inlineStr">
-        <is>
-          <t>E | 456呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G15" s="17" t="inlineStr">
-        <is>
-          <t>F | 452呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H15" s="17" t="inlineStr">
-        <is>
-          <t>G | 457呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I15" s="17" t="inlineStr">
-        <is>
-          <t>H | 466呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J15" s="18" t="inlineStr">
-        <is>
-          <t>J | 549呎 (2房)
-$1,805万
-$32,880/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>A | 670呎 (3房)
-$2,174万
-$32,455/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>B | 579呎 (2房)
-$1,792万
-$30,959/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>C | 568呎 (3房)
-$1,868万
-$32,879/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="E16" s="17" t="inlineStr">
-        <is>
-          <t>D | 498呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F16" s="17" t="inlineStr">
-        <is>
-          <t>E | 456呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G16" s="17" t="inlineStr">
-        <is>
-          <t>F | 452呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H16" s="17" t="inlineStr">
-        <is>
-          <t>G | 457呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I16" s="17" t="inlineStr">
-        <is>
-          <t>H | 466呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J16" s="18" t="inlineStr">
-        <is>
-          <t>J | 549呎 (2房)
-$1,745万
-$31,783/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>A | 669呎 (3房)
-$2,101万
-$31,401/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>B | 579呎 (2房)
-$1,784万
-$30,805/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>C | 568呎 (3房)
-$1,822万
-$32,086/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E17" s="17" t="inlineStr">
-        <is>
-          <t>D | 498呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F17" s="17" t="inlineStr">
-        <is>
-          <t>E | 456呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G17" s="17" t="inlineStr">
-        <is>
-          <t>F | 452呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H17" s="17" t="inlineStr">
-        <is>
-          <t>G | 457呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I17" s="17" t="inlineStr">
-        <is>
-          <t>H | 466呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J17" s="18" t="inlineStr">
-        <is>
-          <t>J | 549呎 (2房)
-$1,736万
-$31,625/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>A | 669呎 (3房)
-$2,090万
-$31,245/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>B | 579呎 (2房)
-$1,775万
-$30,651/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>C | 569呎 (3房)
-$1,778万
-$31,244/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E18" s="17" t="inlineStr">
-        <is>
-          <t>D | 498呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F18" s="17" t="inlineStr">
-        <is>
-          <t>E | 456呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G18" s="17" t="inlineStr">
-        <is>
-          <t>F | 452呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H18" s="17" t="inlineStr">
-        <is>
-          <t>G | 457呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I18" s="17" t="inlineStr">
-        <is>
-          <t>H | 466呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J18" s="18" t="inlineStr">
-        <is>
-          <t>J | 549呎 (2房)
-$1,728万
-$31,466/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>A | 669呎 (3房)
-$2,104万
-$31,444/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>B | 579呎 (2房)
-$1,766万
-$30,499/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>C | 568呎 (3房)
-$1,769万
-$31,144/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E19" s="17" t="inlineStr">
-        <is>
-          <t>D | 498呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F19" s="17" t="inlineStr">
-        <is>
-          <t>E | 456呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G19" s="17" t="inlineStr">
-        <is>
-          <t>F | 452呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H19" s="17" t="inlineStr">
-        <is>
-          <t>G | 457呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I19" s="17" t="inlineStr">
-        <is>
-          <t>H | 466呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J19" s="18" t="inlineStr">
-        <is>
-          <t>J | 549呎 (2房)
-$1,719万
-$31,311/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>A | 669呎 (3房)
-$2,070万
-$30,934/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>B | 579呎 (2房)
-$1,757万
-$30,347/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>C | 568呎 (3房)
-$1,760万
-$30,988/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E20" s="17" t="inlineStr">
-        <is>
-          <t>D | 498呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F20" s="17" t="inlineStr">
-        <is>
-          <t>E | 456呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G20" s="17" t="inlineStr">
-        <is>
-          <t>F | 452呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H20" s="17" t="inlineStr">
-        <is>
-          <t>G | 457呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I20" s="17" t="inlineStr">
-        <is>
-          <t>H | 466呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J20" s="18" t="inlineStr">
-        <is>
-          <t>J | 549呎 (2房)
-$1,694万
-$30,849/呎
-(26年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>A | 670呎 (3房)
-$2,082万
-$31,082/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>B | 579呎 (2房)
-$1,748万
-$30,195/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>C | 568呎 (3房)
-$1,791万
-$31,533/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E21" s="17" t="inlineStr">
-        <is>
-          <t>D | 498呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F21" s="17" t="inlineStr">
-        <is>
-          <t>E | 456呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G21" s="17" t="inlineStr">
-        <is>
-          <t>F | 452呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H21" s="17" t="inlineStr">
-        <is>
-          <t>G | 457呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I21" s="17" t="inlineStr">
-        <is>
-          <t>H | 466呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J21" s="18" t="inlineStr">
-        <is>
-          <t>J | 549呎 (2房)
-$1,685万
-$30,694/呎
-(26年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>A | 669呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>B | 579呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="inlineStr">
-        <is>
-          <t>C | 569呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E22" s="17" t="inlineStr">
-        <is>
-          <t>D | 498呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F22" s="17" t="inlineStr">
-        <is>
-          <t>E | 456呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G22" s="17" t="inlineStr">
-        <is>
-          <t>F | 452呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H22" s="17" t="inlineStr">
-        <is>
-          <t>G | 457呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I22" s="17" t="inlineStr">
-        <is>
-          <t>H | 466呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J22" s="17" t="inlineStr">
-        <is>
-          <t>J | 549呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>A | 669呎 (3房)
-$2,028万
-$30,318/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>B | 579呎 (2房)
-$1,722万
-$29,743/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>C | 569呎 (3房)
-$1,725万
-$30,318/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E23" s="17" t="inlineStr">
-        <is>
-          <t>D | 498呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F23" s="17" t="inlineStr">
-        <is>
-          <t>E | 456呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G23" s="17" t="inlineStr">
-        <is>
-          <t>F | 452呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H23" s="17" t="inlineStr">
-        <is>
-          <t>G | 457呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I23" s="17" t="inlineStr">
-        <is>
-          <t>H | 466呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J23" s="18" t="inlineStr">
-        <is>
-          <t>J | 549呎 (2房)
-$1,676万
-$30,534/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>A | 669呎 (3房)
-$2,018万
-$30,167/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="inlineStr">
-        <is>
-          <t>B | 579呎 (2房)
-$1,714万
-$29,594/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>C | 568呎 (3房)
-$1,716万
-$30,220/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E24" s="17" t="inlineStr">
-        <is>
-          <t>D | 498呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F24" s="17" t="inlineStr">
-        <is>
-          <t>E | 456呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G24" s="17" t="inlineStr">
-        <is>
-          <t>F | 452呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H24" s="17" t="inlineStr">
-        <is>
-          <t>G | 457呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I24" s="17" t="inlineStr">
-        <is>
-          <t>H | 466呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J24" s="18" t="inlineStr">
-        <is>
-          <t>J | 549呎 (2房)
-$1,668万
-$30,383/呎
-(26年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="inlineStr">
-        <is>
-          <t>A | 669呎 (3房)
-$2,008万
-$30,016/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>B | 579呎 (2房)
-$1,724万
-$29,781/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D25" s="18" t="inlineStr">
-        <is>
-          <t>C | 568呎 (3房)
-$1,708万
-$30,069/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E25" s="17" t="inlineStr">
-        <is>
-          <t>D | 498呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F25" s="17" t="inlineStr">
-        <is>
-          <t>E | 456呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G25" s="17" t="inlineStr">
-        <is>
-          <t>F | 452呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H25" s="17" t="inlineStr">
-        <is>
-          <t>G | 457呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I25" s="17" t="inlineStr">
-        <is>
-          <t>H | 466呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J25" s="18" t="inlineStr">
-        <is>
-          <t>J | 549呎 (2房)
-$1,681万
-$30,614/呎
-(26年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B26" s="18" t="inlineStr">
-        <is>
-          <t>A | 669呎 (3房)
-$1,998万
-$29,867/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="inlineStr">
-        <is>
-          <t>B | 579呎 (2房)
-$1,696万
-$29,299/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D26" s="18" t="inlineStr">
-        <is>
-          <t>C | 569呎 (3房)
-$1,699万
-$29,866/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E26" s="17" t="inlineStr">
-        <is>
-          <t>D | 498呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F26" s="17" t="inlineStr">
-        <is>
-          <t>E | 456呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G26" s="17" t="inlineStr">
-        <is>
-          <t>F | 452呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H26" s="17" t="inlineStr">
-        <is>
-          <t>G | 457呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I26" s="17" t="inlineStr">
-        <is>
-          <t>H | 466呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J26" s="18" t="inlineStr">
-        <is>
-          <t>J | 549呎 (2房)
-$1,635万
-$29,783/呎
-(26年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B27" s="18" t="inlineStr">
-        <is>
-          <t>A | 670呎 (3房)
-$2,048万
-$30,564/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C27" s="18" t="inlineStr">
-        <is>
-          <t>B | 579呎 (2房)
-$1,688万
-$29,152/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="D27" s="18" t="inlineStr">
-        <is>
-          <t>C | 569呎 (3房)
-$1,729万
-$30,392/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E27" s="17" t="inlineStr">
-        <is>
-          <t>D | 498呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F27" s="17" t="inlineStr">
-        <is>
-          <t>E | 456呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G27" s="17" t="inlineStr">
-        <is>
-          <t>F | 452呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H27" s="17" t="inlineStr">
-        <is>
-          <t>G | 457呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I27" s="17" t="inlineStr">
-        <is>
-          <t>H | 466呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J27" s="18" t="inlineStr">
-        <is>
-          <t>J | 549呎 (2房)
-$1,611万
-$29,341/呎
-(26年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B28" s="18" t="inlineStr">
-        <is>
-          <t>A | 669呎 (3房)
-$1,978万
-$29,568/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C28" s="18" t="inlineStr">
-        <is>
-          <t>B | 579呎 (2房)
-$1,680万
-$29,007/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="D28" s="18" t="inlineStr">
-        <is>
-          <t>C | 568呎 (3房)
-$1,682万
-$29,620/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E28" s="17" t="inlineStr">
-        <is>
-          <t>D | 498呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F28" s="17" t="inlineStr">
-        <is>
-          <t>E | 456呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G28" s="17" t="inlineStr">
-        <is>
-          <t>F | 452呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H28" s="17" t="inlineStr">
-        <is>
-          <t>G | 457呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I28" s="17" t="inlineStr">
-        <is>
-          <t>H | 466呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J28" s="18" t="inlineStr">
-        <is>
-          <t>J | 549呎 (2房)
-$1,603万
-$29,195/呎
-(26年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B29" s="18" t="inlineStr">
-        <is>
-          <t>A | 669呎 (3房)
-$1,968万
-$29,420/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C29" s="18" t="inlineStr">
-        <is>
-          <t>B | 579呎 (2房)
-$1,671万
-$28,862/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="D29" s="18" t="inlineStr">
-        <is>
-          <t>C | 568呎 (3房)
-$1,674万
-$29,472/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E29" s="17" t="inlineStr">
-        <is>
-          <t>D | 498呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F29" s="17" t="inlineStr">
-        <is>
-          <t>E | 456呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G29" s="17" t="inlineStr">
-        <is>
-          <t>F | 452呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H29" s="17" t="inlineStr">
-        <is>
-          <t>G | 457呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I29" s="17" t="inlineStr">
-        <is>
-          <t>H | 466呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J29" s="18" t="inlineStr">
-        <is>
-          <t>J | 549呎 (2房)
-$1,611万
-$29,339/呎
-(26年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B30" s="18" t="inlineStr">
-        <is>
-          <t>A | 669呎 (3房)
-$1,958万
-$29,269/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C30" s="18" t="inlineStr">
-        <is>
-          <t>B | 579呎 (2房)
-$1,646万
-$28,428/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D30" s="18" t="inlineStr">
-        <is>
-          <t>C | 568呎 (3房)
-$1,649万
-$29,030/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E30" s="17" t="inlineStr">
-        <is>
-          <t>D | 498呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F30" s="17" t="inlineStr">
-        <is>
-          <t>E | 456呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G30" s="17" t="inlineStr">
-        <is>
-          <t>F | 452呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H30" s="17" t="inlineStr">
-        <is>
-          <t>G | 457呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I30" s="17" t="inlineStr">
-        <is>
-          <t>H | 466呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J30" s="18" t="inlineStr">
-        <is>
-          <t>J | 549呎 (2房)
-$1,571万
-$28,612/呎
-(26年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B31" s="18" t="inlineStr">
-        <is>
-          <t>A | 670呎 (3房)
-$1,941万
-$28,972/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C31" s="18" t="inlineStr">
-        <is>
-          <t>B | 579呎 (2房)
-$1,630万
-$28,145/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="D31" s="18" t="inlineStr">
-        <is>
-          <t>C | 568呎 (3房)
-$1,632万
-$28,739/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E31" s="17" t="inlineStr">
-        <is>
-          <t>D | 498呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F31" s="17" t="inlineStr">
-        <is>
-          <t>E | 456呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G31" s="17" t="inlineStr">
-        <is>
-          <t>F | 452呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H31" s="17" t="inlineStr">
-        <is>
-          <t>G | 457呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I31" s="17" t="inlineStr">
-        <is>
-          <t>H | 466呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J31" s="18" t="inlineStr">
-        <is>
-          <t>J | 549呎 (2房)
-$1,573万
-$28,648/呎
-(26年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B32" s="18" t="inlineStr">
-        <is>
-          <t>A | 670呎 (3房)
-$1,902万
-$28,385/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C32" s="18" t="inlineStr">
-        <is>
-          <t>B | 579呎 (2房)
-$1,650万
-$28,496/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="D32" s="18" t="inlineStr">
-        <is>
-          <t>C | 568呎 (3房)
-$1,617万
-$28,468/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E32" s="17" t="inlineStr">
-        <is>
-          <t>D | 498呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F32" s="17" t="inlineStr">
-        <is>
-          <t>E | 458呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G32" s="20" t="inlineStr"/>
-      <c r="H32" s="17" t="inlineStr">
-        <is>
-          <t>G | 467呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I32" s="17" t="inlineStr">
-        <is>
-          <t>H | 466呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J32" s="18" t="inlineStr">
-        <is>
-          <t>J | 549呎 (2房)
-$1,555万
-$28,324/呎
-(26年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B33" s="18" t="inlineStr">
-        <is>
-          <t>A | 639呎 (2房)
-$1,788万
-$27,977/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C33" s="20" t="inlineStr"/>
-      <c r="D33" s="20" t="inlineStr"/>
-      <c r="E33" s="20" t="inlineStr"/>
-      <c r="F33" s="20" t="inlineStr"/>
-      <c r="G33" s="20" t="inlineStr"/>
-      <c r="H33" s="17" t="inlineStr">
-        <is>
-          <t>G | 460呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I33" s="17" t="inlineStr">
-        <is>
-          <t>H | 466呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J33" s="18" t="inlineStr">
-        <is>
-          <t>J | 549呎 (2房)
-$1,516万
-$27,623/呎
-(26年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B34" s="18" t="inlineStr">
-        <is>
-          <t>A | 639呎 (2房)
-$1,761万
-$27,557/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C34" s="20" t="inlineStr"/>
-      <c r="D34" s="20" t="inlineStr"/>
-      <c r="E34" s="20" t="inlineStr"/>
-      <c r="F34" s="20" t="inlineStr"/>
-      <c r="G34" s="20" t="inlineStr"/>
-      <c r="H34" s="17" t="inlineStr">
-        <is>
-          <t>G | 460呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I34" s="17" t="inlineStr">
-        <is>
-          <t>H | 466呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J34" s="18" t="inlineStr">
-        <is>
-          <t>J | 549呎 (2房)
-$1,494万
-$27,208/呎
-(26年-03月)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/九龙-启德-维港．湾畔第1B期.xlsx
+++ b/files/九龙-启德-维港．湾畔第1B期.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2A座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2B座" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +43,101 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +148,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +229,63 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +662,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -25395,4 +25583,4815 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2A座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 557呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>B | 565呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>C | 450呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>D | 300呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G5" s="21" t="inlineStr">
+        <is>
+          <t>F | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H5" s="21" t="inlineStr">
+        <is>
+          <t>G | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I5" s="21" t="inlineStr">
+        <is>
+          <t>H | 309呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J5" s="21" t="inlineStr">
+        <is>
+          <t>J | 559呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 560呎 (2房)
+$1921万
+$34,307/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 516呎 (2房)
+$1742万
+$33,756/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 450呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 300呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>F | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t>G | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I6" s="21" t="inlineStr">
+        <is>
+          <t>H | 309呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J6" s="21" t="inlineStr">
+        <is>
+          <t>J | 559呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 560呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 516呎 (2房)
+$1692万
+$32,791/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>C | 450呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>D | 300呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G7" s="21" t="inlineStr">
+        <is>
+          <t>F | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t>G | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I7" s="21" t="inlineStr">
+        <is>
+          <t>H | 309呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J7" s="21" t="inlineStr">
+        <is>
+          <t>J | 559呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 560呎 (2房)
+$1848万
+$32,993/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 516呎 (2房)
+$1675万
+$32,467/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>C | 450呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>D | 300呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G8" s="21" t="inlineStr">
+        <is>
+          <t>F | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t>G | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I8" s="21" t="inlineStr">
+        <is>
+          <t>H | 309呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J8" s="21" t="inlineStr">
+        <is>
+          <t>J | 559呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 560呎 (2房)
+$1794万
+$32,030/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 516呎 (2房)
+$1627万
+$31,527/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>C | 450呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>D | 300呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G9" s="21" t="inlineStr">
+        <is>
+          <t>F | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t>G | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I9" s="21" t="inlineStr">
+        <is>
+          <t>H | 309呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J9" s="21" t="inlineStr">
+        <is>
+          <t>J | 559呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 560呎 (2房)
+$1776万
+$31,714/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 516呎 (2房)
+$1611万
+$31,215/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>C | 450呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>D | 300呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G10" s="21" t="inlineStr">
+        <is>
+          <t>F | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t>G | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I10" s="21" t="inlineStr">
+        <is>
+          <t>H | 309呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J10" s="21" t="inlineStr">
+        <is>
+          <t>J | 559呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 560呎 (2房)
+$1758万
+$31,400/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 516呎 (2房)
+$1595万
+$30,907/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>C | 450呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>D | 300呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G11" s="21" t="inlineStr">
+        <is>
+          <t>F | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t>G | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I11" s="21" t="inlineStr">
+        <is>
+          <t>H | 309呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J11" s="21" t="inlineStr">
+        <is>
+          <t>J | 559呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 560呎 (2房)
+$1743万
+$31,130/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 516呎 (2房)
+$1548万
+$30,000/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>C | 450呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>D | 300呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G12" s="21" t="inlineStr">
+        <is>
+          <t>F | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t>G | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I12" s="21" t="inlineStr">
+        <is>
+          <t>H | 309呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J12" s="21" t="inlineStr">
+        <is>
+          <t>J | 559呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 560呎 (2房)
+$1715万
+$30,627/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 516呎 (2房)
+$1540万
+$29,851/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>C | 450呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>D | 300呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G13" s="21" t="inlineStr">
+        <is>
+          <t>F | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t>G | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I13" s="21" t="inlineStr">
+        <is>
+          <t>H | 309呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J13" s="21" t="inlineStr">
+        <is>
+          <t>J | 559呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 560呎 (2房)
+$1707万
+$30,475/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 516呎 (2房)
+$1533万
+$29,702/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>C | 450呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>D | 300呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G14" s="21" t="inlineStr">
+        <is>
+          <t>F | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H14" s="21" t="inlineStr">
+        <is>
+          <t>G | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I14" s="21" t="inlineStr">
+        <is>
+          <t>H | 309呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J14" s="21" t="inlineStr">
+        <is>
+          <t>J | 559呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 560呎 (2房)
+$1715万
+$30,627/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 516呎 (2房)
+$1525万
+$29,554/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>C | 450呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>D | 300呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G15" s="21" t="inlineStr">
+        <is>
+          <t>F | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H15" s="21" t="inlineStr">
+        <is>
+          <t>G | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I15" s="21" t="inlineStr">
+        <is>
+          <t>H | 309呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J15" s="21" t="inlineStr">
+        <is>
+          <t>J | 559呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 560呎 (2房)
+$1707万
+$30,475/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 516呎 (2房)
+$1517万
+$29,407/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>C | 450呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>D | 300呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G16" s="21" t="inlineStr">
+        <is>
+          <t>F | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H16" s="21" t="inlineStr">
+        <is>
+          <t>G | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I16" s="21" t="inlineStr">
+        <is>
+          <t>H | 309呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J16" s="20" t="inlineStr">
+        <is>
+          <t>J | 559呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 560呎 (2房)
+$1681万
+$30,023/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 516呎 (2房)
+$1510万
+$29,260/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>C | 450呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>D | 300呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G17" s="21" t="inlineStr">
+        <is>
+          <t>F | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H17" s="21" t="inlineStr">
+        <is>
+          <t>G | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I17" s="21" t="inlineStr">
+        <is>
+          <t>H | 309呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J17" s="22" t="inlineStr">
+        <is>
+          <t>J | 559呎 (2房)
+$1832万
+$32,771/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 560呎 (2房)
+$1673万
+$29,873/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 516呎 (2房)
+$1502万
+$29,114/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>C | 450呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>D | 300呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G18" s="21" t="inlineStr">
+        <is>
+          <t>F | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H18" s="21" t="inlineStr">
+        <is>
+          <t>G | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I18" s="21" t="inlineStr">
+        <is>
+          <t>H | 309呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J18" s="22" t="inlineStr">
+        <is>
+          <t>J | 559呎 (2房)
+$1823万
+$32,610/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 560呎 (2房)
+$1664万
+$29,723/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 516呎 (2房)
+$1495万
+$28,969/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>C | 450呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>D | 300呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F19" s="21" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G19" s="21" t="inlineStr">
+        <is>
+          <t>F | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H19" s="21" t="inlineStr">
+        <is>
+          <t>G | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I19" s="21" t="inlineStr">
+        <is>
+          <t>H | 309呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J19" s="22" t="inlineStr">
+        <is>
+          <t>J | 559呎 (2房)
+$1780万
+$31,844/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 560呎 (2房)
+$1694万
+$30,246/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 516呎 (2房)
+$1487万
+$28,826/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>C | 450呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>D | 300呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G20" s="21" t="inlineStr">
+        <is>
+          <t>F | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H20" s="21" t="inlineStr">
+        <is>
+          <t>G | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I20" s="21" t="inlineStr">
+        <is>
+          <t>H | 309呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J20" s="22" t="inlineStr">
+        <is>
+          <t>J | 559呎 (2房)
+$1805万
+$32,283/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>A | 560呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>B | 516呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>C | 450呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>D | 300呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G21" s="21" t="inlineStr">
+        <is>
+          <t>F | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H21" s="21" t="inlineStr">
+        <is>
+          <t>G | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I21" s="21" t="inlineStr">
+        <is>
+          <t>H | 309呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J21" s="21" t="inlineStr">
+        <is>
+          <t>J | 559呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 560呎 (2房)
+$1631万
+$29,132/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 516呎 (2房)
+$1465万
+$28,393/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr">
+        <is>
+          <t>C | 450呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>D | 300呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G22" s="21" t="inlineStr">
+        <is>
+          <t>F | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H22" s="21" t="inlineStr">
+        <is>
+          <t>G | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I22" s="21" t="inlineStr">
+        <is>
+          <t>H | 309呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J22" s="22" t="inlineStr">
+        <is>
+          <t>J | 559呎 (2房)
+$1734万
+$31,018/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>A | 560呎 (2房)
+$1623万
+$28,988/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B | 516呎 (2房)
+$1458万
+$28,252/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr">
+        <is>
+          <t>C | 450呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="inlineStr">
+        <is>
+          <t>D | 300呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G23" s="21" t="inlineStr">
+        <is>
+          <t>F | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H23" s="21" t="inlineStr">
+        <is>
+          <t>G | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I23" s="21" t="inlineStr">
+        <is>
+          <t>H | 309呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J23" s="22" t="inlineStr">
+        <is>
+          <t>J | 559呎 (2房)
+$1759万
+$31,460/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>A | 560呎 (2房)
+$1615万
+$28,843/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 516呎 (2房)
+$1450万
+$28,110/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
+        <is>
+          <t>C | 450呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>D | 300呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
+        <is>
+          <t>F | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H24" s="21" t="inlineStr">
+        <is>
+          <t>G | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I24" s="21" t="inlineStr">
+        <is>
+          <t>H | 309呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J24" s="22" t="inlineStr">
+        <is>
+          <t>J | 559呎 (2房)
+$1711万
+$30,608/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>A | 560呎 (2房)
+$1607万
+$28,698/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>B | 516呎 (2房)
+$1443万
+$27,969/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D25" s="21" t="inlineStr">
+        <is>
+          <t>C | 450呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>D | 300呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G25" s="21" t="inlineStr">
+        <is>
+          <t>F | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H25" s="21" t="inlineStr">
+        <is>
+          <t>G | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I25" s="21" t="inlineStr">
+        <is>
+          <t>H | 309呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J25" s="22" t="inlineStr">
+        <is>
+          <t>J | 559呎 (2房)
+$1758万
+$31,444/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>A | 560呎 (2房)
+$1599万
+$28,555/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>B | 516呎 (2房)
+$1436万
+$27,829/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D26" s="21" t="inlineStr">
+        <is>
+          <t>C | 450呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E26" s="21" t="inlineStr">
+        <is>
+          <t>D | 300呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F26" s="21" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G26" s="21" t="inlineStr">
+        <is>
+          <t>F | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H26" s="21" t="inlineStr">
+        <is>
+          <t>G | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I26" s="21" t="inlineStr">
+        <is>
+          <t>H | 309呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J26" s="22" t="inlineStr">
+        <is>
+          <t>J | 559呎 (2房)
+$1710万
+$30,592/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>A | 560呎 (2房)
+$1591万
+$28,412/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>B | 516呎 (2房)
+$1429万
+$27,692/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D27" s="21" t="inlineStr">
+        <is>
+          <t>C | 450呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E27" s="21" t="inlineStr">
+        <is>
+          <t>D | 300呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G27" s="21" t="inlineStr">
+        <is>
+          <t>F | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H27" s="21" t="inlineStr">
+        <is>
+          <t>G | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I27" s="21" t="inlineStr">
+        <is>
+          <t>H | 309呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J27" s="22" t="inlineStr">
+        <is>
+          <t>J | 559呎 (2房)
+$1702万
+$30,440/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>A | 560呎 (2房)
+$1583万
+$28,270/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>B | 516呎 (2房)
+$1422万
+$27,552/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D28" s="21" t="inlineStr">
+        <is>
+          <t>C | 450呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E28" s="21" t="inlineStr">
+        <is>
+          <t>D | 300呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F28" s="21" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G28" s="21" t="inlineStr">
+        <is>
+          <t>F | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H28" s="21" t="inlineStr">
+        <is>
+          <t>G | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I28" s="21" t="inlineStr">
+        <is>
+          <t>H | 309呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J28" s="22" t="inlineStr">
+        <is>
+          <t>J | 559呎 (2房)
+$1693万
+$30,288/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
+        <is>
+          <t>A | 560呎 (2房)
+$1559万
+$27,846/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="inlineStr">
+        <is>
+          <t>B | 516呎 (2房)
+$1400万
+$27,140/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D29" s="21" t="inlineStr">
+        <is>
+          <t>C | 450呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E29" s="21" t="inlineStr">
+        <is>
+          <t>D | 300呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F29" s="21" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G29" s="21" t="inlineStr">
+        <is>
+          <t>F | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H29" s="21" t="inlineStr">
+        <is>
+          <t>G | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I29" s="21" t="inlineStr">
+        <is>
+          <t>H | 309呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J29" s="22" t="inlineStr">
+        <is>
+          <t>J | 559呎 (2房)
+$1652万
+$29,551/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>A | 560呎 (2房)
+$1579万
+$28,195/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C30" s="22" t="inlineStr">
+        <is>
+          <t>B | 516呎 (2房)
+$1386万
+$26,868/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D30" s="21" t="inlineStr">
+        <is>
+          <t>C | 450呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E30" s="21" t="inlineStr">
+        <is>
+          <t>D | 300呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F30" s="21" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G30" s="21" t="inlineStr">
+        <is>
+          <t>F | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H30" s="21" t="inlineStr">
+        <is>
+          <t>G | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I30" s="21" t="inlineStr">
+        <is>
+          <t>H | 309呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J30" s="22" t="inlineStr">
+        <is>
+          <t>J | 559呎 (2房)
+$1620万
+$28,977/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>A | 560呎 (2房)
+$1528万
+$27,291/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C31" s="22" t="inlineStr">
+        <is>
+          <t>B | 516呎 (2房)
+$1372万
+$26,599/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D31" s="21" t="inlineStr">
+        <is>
+          <t>C | 450呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E31" s="21" t="inlineStr">
+        <is>
+          <t>D | 300呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F31" s="21" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G31" s="21" t="inlineStr">
+        <is>
+          <t>F | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H31" s="21" t="inlineStr">
+        <is>
+          <t>G | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I31" s="21" t="inlineStr">
+        <is>
+          <t>H | 309呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J31" s="22" t="inlineStr">
+        <is>
+          <t>J | 559呎 (2房)
+$1619万
+$28,962/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="inlineStr">
+        <is>
+          <t>A | 560呎 (2房)
+$1540万
+$27,493/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="inlineStr">
+        <is>
+          <t>B | 516呎 (2房)
+$1352万
+$26,200/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D32" s="21" t="inlineStr">
+        <is>
+          <t>C | 450呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E32" s="21" t="inlineStr">
+        <is>
+          <t>D | 300呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F32" s="21" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G32" s="21" t="inlineStr">
+        <is>
+          <t>F | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H32" s="21" t="inlineStr">
+        <is>
+          <t>G | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I32" s="21" t="inlineStr">
+        <is>
+          <t>H | 309呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J32" s="22" t="inlineStr">
+        <is>
+          <t>J | 559呎 (2房)
+$1580万
+$28,258/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="inlineStr">
+        <is>
+          <t>A | 560呎 (2房)
+$1483万
+$26,488/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C33" s="22" t="inlineStr">
+        <is>
+          <t>B | 516呎 (2房)
+$1333万
+$25,828/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D33" s="21" t="inlineStr">
+        <is>
+          <t>C | 450呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E33" s="21" t="inlineStr">
+        <is>
+          <t>D | 300呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F33" s="21" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G33" s="21" t="inlineStr">
+        <is>
+          <t>F | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H33" s="21" t="inlineStr">
+        <is>
+          <t>G | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I33" s="21" t="inlineStr">
+        <is>
+          <t>H | 309呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J33" s="22" t="inlineStr">
+        <is>
+          <t>J | 559呎 (2房)
+$1586万
+$28,369/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2B座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>A | 670呎 (3房)
+$2424万
+$36,187/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>B | 592呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>C | 568呎 (3房)
+$2117万
+$37,276/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>D | 498呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t>E | 456呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G5" s="21" t="inlineStr">
+        <is>
+          <t>F | 452呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H5" s="21" t="inlineStr">
+        <is>
+          <t>G | 457呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I5" s="21" t="inlineStr">
+        <is>
+          <t>H | 466呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J5" s="23" t="inlineStr">
+        <is>
+          <t>J | 549呎 (2房)
+$2126万
+$38,727/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 670呎 (3房)
+$2320万
+$34,634/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 579呎 (2房)
+$2047万
+$35,361/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>C | 568呎 (3房)
+$1993万
+$35,086/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 498呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t>E | 456呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>F | 452呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t>G | 457呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I6" s="21" t="inlineStr">
+        <is>
+          <t>H | 466呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J6" s="23" t="inlineStr">
+        <is>
+          <t>J | 549呎 (2房)
+$2095万
+$38,153/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 670呎 (3房)
+$2298万
+$34,291/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 579呎 (2房)
+$1956万
+$33,777/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 568呎 (3房)
+$2050万
+$36,088/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>D | 498呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t>E | 456呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G7" s="21" t="inlineStr">
+        <is>
+          <t>F | 452呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t>G | 457呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I7" s="21" t="inlineStr">
+        <is>
+          <t>H | 466呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J7" s="22" t="inlineStr">
+        <is>
+          <t>J | 549呎 (2房)
+$1825万
+$33,242/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 670呎 (3房)
+$2275万
+$33,952/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 579呎 (2房)
+$1931万
+$33,356/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>C | 568呎 (3房)
+$2086万
+$36,732/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>D | 498呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t>E | 456呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G8" s="21" t="inlineStr">
+        <is>
+          <t>F | 452呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t>G | 457呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I8" s="21" t="inlineStr">
+        <is>
+          <t>H | 466呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J8" s="20" t="inlineStr">
+        <is>
+          <t>J | 549呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 670呎 (3房)
+$2252万
+$33,613/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 579呎 (2房)
+$1912万
+$33,026/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>C | 568呎 (3房)
+$1972万
+$34,715/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>D | 498呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>E | 456呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G9" s="21" t="inlineStr">
+        <is>
+          <t>F | 452呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t>G | 457呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I9" s="21" t="inlineStr">
+        <is>
+          <t>H | 466呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J9" s="22" t="inlineStr">
+        <is>
+          <t>J | 549呎 (2房)
+$1878万
+$34,217/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 670呎 (3房)
+$2230万
+$33,282/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 579呎 (2房)
+$1968万
+$33,981/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>C | 568呎 (3房)
+$1952万
+$34,371/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>D | 498呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t>E | 456呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G10" s="21" t="inlineStr">
+        <is>
+          <t>F | 452呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t>G | 457呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I10" s="21" t="inlineStr">
+        <is>
+          <t>H | 466呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J10" s="23" t="inlineStr">
+        <is>
+          <t>J | 549呎 (2房)
+$2013万
+$36,665/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 670呎 (3房)
+$2186万
+$32,630/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 579呎 (2房)
+$1948万
+$33,644/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>C | 568呎 (3房)
+$1915万
+$33,708/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>D | 498呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>E | 456呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G11" s="21" t="inlineStr">
+        <is>
+          <t>F | 452呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t>G | 457呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I11" s="21" t="inlineStr">
+        <is>
+          <t>H | 466呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J11" s="22" t="inlineStr">
+        <is>
+          <t>J | 549呎 (2房)
+$1789万
+$32,583/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 669呎 (3房)
+$2143万
+$32,033/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 579呎 (2房)
+$1856万
+$32,054/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>C | 568呎 (3房)
+$1859万
+$32,732/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>D | 498呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t>E | 456呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G12" s="21" t="inlineStr">
+        <is>
+          <t>F | 452呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t>G | 457呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I12" s="21" t="inlineStr">
+        <is>
+          <t>H | 466呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J12" s="22" t="inlineStr">
+        <is>
+          <t>J | 549呎 (2房)
+$1791万
+$32,630/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 669呎 (3房)
+$2132万
+$31,874/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 579呎 (2房)
+$1831万
+$31,623/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 568呎 (3房)
+$1814万
+$31,930/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>D | 498呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t>E | 456呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G13" s="21" t="inlineStr">
+        <is>
+          <t>F | 452呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t>G | 457呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I13" s="21" t="inlineStr">
+        <is>
+          <t>H | 466呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J13" s="23" t="inlineStr">
+        <is>
+          <t>J | 549呎 (2房)
+$1963万
+$35,761/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 669呎 (3房)
+$2192万
+$32,762/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 579呎 (2房)
+$1802万
+$31,114/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 568呎 (3房)
+$1841万
+$32,407/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>D | 498呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t>E | 456呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G14" s="21" t="inlineStr">
+        <is>
+          <t>F | 452呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H14" s="21" t="inlineStr">
+        <is>
+          <t>G | 457呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I14" s="21" t="inlineStr">
+        <is>
+          <t>H | 466呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J14" s="22" t="inlineStr">
+        <is>
+          <t>J | 549呎 (2房)
+$1805万
+$32,880/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 670呎 (3房)
+$2174万
+$32,455/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 579呎 (2房)
+$1792万
+$30,959/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 568呎 (3房)
+$1868万
+$32,879/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>D | 498呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr">
+        <is>
+          <t>E | 456呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G15" s="21" t="inlineStr">
+        <is>
+          <t>F | 452呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H15" s="21" t="inlineStr">
+        <is>
+          <t>G | 457呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I15" s="21" t="inlineStr">
+        <is>
+          <t>H | 466呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J15" s="22" t="inlineStr">
+        <is>
+          <t>J | 549呎 (2房)
+$1745万
+$31,783/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 669呎 (3房)
+$2101万
+$31,401/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 579呎 (2房)
+$1784万
+$30,805/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>C | 568呎 (3房)
+$1822万
+$32,086/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>D | 498呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
+        <is>
+          <t>E | 456呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G16" s="21" t="inlineStr">
+        <is>
+          <t>F | 452呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H16" s="21" t="inlineStr">
+        <is>
+          <t>G | 457呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I16" s="21" t="inlineStr">
+        <is>
+          <t>H | 466呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J16" s="22" t="inlineStr">
+        <is>
+          <t>J | 549呎 (2房)
+$1736万
+$31,625/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 669呎 (3房)
+$2090万
+$31,245/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 579呎 (2房)
+$1775万
+$30,651/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>C | 569呎 (3房)
+$1778万
+$31,244/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>D | 498呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr">
+        <is>
+          <t>E | 456呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G17" s="21" t="inlineStr">
+        <is>
+          <t>F | 452呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H17" s="21" t="inlineStr">
+        <is>
+          <t>G | 457呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I17" s="21" t="inlineStr">
+        <is>
+          <t>H | 466呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J17" s="22" t="inlineStr">
+        <is>
+          <t>J | 549呎 (2房)
+$1728万
+$31,466/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 669呎 (3房)
+$2104万
+$31,444/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 579呎 (2房)
+$1766万
+$30,499/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>C | 568呎 (3房)
+$1769万
+$31,144/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>D | 498呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="inlineStr">
+        <is>
+          <t>E | 456呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G18" s="21" t="inlineStr">
+        <is>
+          <t>F | 452呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H18" s="21" t="inlineStr">
+        <is>
+          <t>G | 457呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I18" s="21" t="inlineStr">
+        <is>
+          <t>H | 466呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J18" s="22" t="inlineStr">
+        <is>
+          <t>J | 549呎 (2房)
+$1719万
+$31,311/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 669呎 (3房)
+$2070万
+$30,934/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 579呎 (2房)
+$1757万
+$30,347/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>C | 568呎 (3房)
+$1760万
+$30,988/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>D | 498呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F19" s="21" t="inlineStr">
+        <is>
+          <t>E | 456呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G19" s="21" t="inlineStr">
+        <is>
+          <t>F | 452呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H19" s="21" t="inlineStr">
+        <is>
+          <t>G | 457呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I19" s="21" t="inlineStr">
+        <is>
+          <t>H | 466呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J19" s="22" t="inlineStr">
+        <is>
+          <t>J | 549呎 (2房)
+$1694万
+$30,849/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 670呎 (3房)
+$2082万
+$31,082/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 579呎 (2房)
+$1748万
+$30,195/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 568呎 (3房)
+$1791万
+$31,533/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>D | 498呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="inlineStr">
+        <is>
+          <t>E | 456呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G20" s="21" t="inlineStr">
+        <is>
+          <t>F | 452呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H20" s="21" t="inlineStr">
+        <is>
+          <t>G | 457呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I20" s="21" t="inlineStr">
+        <is>
+          <t>H | 466呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J20" s="22" t="inlineStr">
+        <is>
+          <t>J | 549呎 (2房)
+$1685万
+$30,694/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>A | 669呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>B | 579呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>C | 569呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>D | 498呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t>E | 456呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G21" s="21" t="inlineStr">
+        <is>
+          <t>F | 452呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H21" s="21" t="inlineStr">
+        <is>
+          <t>G | 457呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I21" s="21" t="inlineStr">
+        <is>
+          <t>H | 466呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J21" s="21" t="inlineStr">
+        <is>
+          <t>J | 549呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 669呎 (3房)
+$2028万
+$30,318/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 579呎 (2房)
+$1722万
+$29,743/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 569呎 (3房)
+$1725万
+$30,318/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>D | 498呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="inlineStr">
+        <is>
+          <t>E | 456呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G22" s="21" t="inlineStr">
+        <is>
+          <t>F | 452呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H22" s="21" t="inlineStr">
+        <is>
+          <t>G | 457呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I22" s="21" t="inlineStr">
+        <is>
+          <t>H | 466呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J22" s="22" t="inlineStr">
+        <is>
+          <t>J | 549呎 (2房)
+$1676万
+$30,534/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>A | 669呎 (3房)
+$2018万
+$30,167/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B | 579呎 (2房)
+$1714万
+$29,594/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>C | 568呎 (3房)
+$1716万
+$30,220/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="inlineStr">
+        <is>
+          <t>D | 498呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="inlineStr">
+        <is>
+          <t>E | 456呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G23" s="21" t="inlineStr">
+        <is>
+          <t>F | 452呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H23" s="21" t="inlineStr">
+        <is>
+          <t>G | 457呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I23" s="21" t="inlineStr">
+        <is>
+          <t>H | 466呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J23" s="22" t="inlineStr">
+        <is>
+          <t>J | 549呎 (2房)
+$1668万
+$30,383/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>A | 669呎 (3房)
+$2008万
+$30,016/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 579呎 (2房)
+$1724万
+$29,781/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>C | 568呎 (3房)
+$1708万
+$30,069/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>D | 498呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
+        <is>
+          <t>E | 456呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
+        <is>
+          <t>F | 452呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H24" s="21" t="inlineStr">
+        <is>
+          <t>G | 457呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I24" s="21" t="inlineStr">
+        <is>
+          <t>H | 466呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J24" s="22" t="inlineStr">
+        <is>
+          <t>J | 549呎 (2房)
+$1681万
+$30,614/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>A | 669呎 (3房)
+$1998万
+$29,867/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>B | 579呎 (2房)
+$1696万
+$29,299/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>C | 569呎 (3房)
+$1699万
+$29,866/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>D | 498呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="inlineStr">
+        <is>
+          <t>E | 456呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G25" s="21" t="inlineStr">
+        <is>
+          <t>F | 452呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H25" s="21" t="inlineStr">
+        <is>
+          <t>G | 457呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I25" s="21" t="inlineStr">
+        <is>
+          <t>H | 466呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J25" s="22" t="inlineStr">
+        <is>
+          <t>J | 549呎 (2房)
+$1635万
+$29,783/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>A | 670呎 (3房)
+$2048万
+$30,564/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>B | 579呎 (2房)
+$1688万
+$29,152/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>C | 569呎 (3房)
+$1729万
+$30,392/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E26" s="21" t="inlineStr">
+        <is>
+          <t>D | 498呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F26" s="21" t="inlineStr">
+        <is>
+          <t>E | 456呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G26" s="21" t="inlineStr">
+        <is>
+          <t>F | 452呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H26" s="21" t="inlineStr">
+        <is>
+          <t>G | 457呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I26" s="21" t="inlineStr">
+        <is>
+          <t>H | 466呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J26" s="22" t="inlineStr">
+        <is>
+          <t>J | 549呎 (2房)
+$1611万
+$29,341/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>A | 669呎 (3房)
+$1978万
+$29,568/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>B | 579呎 (2房)
+$1680万
+$29,007/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>C | 568呎 (3房)
+$1682万
+$29,620/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E27" s="21" t="inlineStr">
+        <is>
+          <t>D | 498呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="inlineStr">
+        <is>
+          <t>E | 456呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G27" s="21" t="inlineStr">
+        <is>
+          <t>F | 452呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H27" s="21" t="inlineStr">
+        <is>
+          <t>G | 457呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I27" s="21" t="inlineStr">
+        <is>
+          <t>H | 466呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J27" s="22" t="inlineStr">
+        <is>
+          <t>J | 549呎 (2房)
+$1603万
+$29,195/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>A | 669呎 (3房)
+$1968万
+$29,420/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>B | 579呎 (2房)
+$1671万
+$28,862/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>C | 568呎 (3房)
+$1674万
+$29,472/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E28" s="21" t="inlineStr">
+        <is>
+          <t>D | 498呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F28" s="21" t="inlineStr">
+        <is>
+          <t>E | 456呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G28" s="21" t="inlineStr">
+        <is>
+          <t>F | 452呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H28" s="21" t="inlineStr">
+        <is>
+          <t>G | 457呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I28" s="21" t="inlineStr">
+        <is>
+          <t>H | 466呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J28" s="22" t="inlineStr">
+        <is>
+          <t>J | 549呎 (2房)
+$1611万
+$29,339/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
+        <is>
+          <t>A | 669呎 (3房)
+$1958万
+$29,269/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="inlineStr">
+        <is>
+          <t>B | 579呎 (2房)
+$1646万
+$28,428/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D29" s="22" t="inlineStr">
+        <is>
+          <t>C | 568呎 (3房)
+$1649万
+$29,030/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E29" s="21" t="inlineStr">
+        <is>
+          <t>D | 498呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F29" s="21" t="inlineStr">
+        <is>
+          <t>E | 456呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G29" s="21" t="inlineStr">
+        <is>
+          <t>F | 452呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H29" s="21" t="inlineStr">
+        <is>
+          <t>G | 457呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I29" s="21" t="inlineStr">
+        <is>
+          <t>H | 466呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J29" s="22" t="inlineStr">
+        <is>
+          <t>J | 549呎 (2房)
+$1571万
+$28,612/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>A | 670呎 (3房)
+$1941万
+$28,972/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C30" s="22" t="inlineStr">
+        <is>
+          <t>B | 579呎 (2房)
+$1630万
+$28,145/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D30" s="22" t="inlineStr">
+        <is>
+          <t>C | 568呎 (3房)
+$1632万
+$28,739/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E30" s="21" t="inlineStr">
+        <is>
+          <t>D | 498呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F30" s="21" t="inlineStr">
+        <is>
+          <t>E | 456呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G30" s="21" t="inlineStr">
+        <is>
+          <t>F | 452呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H30" s="21" t="inlineStr">
+        <is>
+          <t>G | 457呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I30" s="21" t="inlineStr">
+        <is>
+          <t>H | 466呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J30" s="22" t="inlineStr">
+        <is>
+          <t>J | 549呎 (2房)
+$1573万
+$28,648/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>A | 670呎 (3房)
+$1902万
+$28,385/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C31" s="22" t="inlineStr">
+        <is>
+          <t>B | 579呎 (2房)
+$1650万
+$28,496/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="inlineStr">
+        <is>
+          <t>C | 568呎 (3房)
+$1617万
+$28,468/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E31" s="21" t="inlineStr">
+        <is>
+          <t>D | 498呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F31" s="21" t="inlineStr">
+        <is>
+          <t>E | 458呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G31" s="24" t="inlineStr"/>
+      <c r="H31" s="21" t="inlineStr">
+        <is>
+          <t>G | 467呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I31" s="21" t="inlineStr">
+        <is>
+          <t>H | 466呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J31" s="22" t="inlineStr">
+        <is>
+          <t>J | 549呎 (2房)
+$1555万
+$28,324/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="inlineStr">
+        <is>
+          <t>A | 639呎 (2房)
+$1788万
+$27,977/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C32" s="24" t="inlineStr"/>
+      <c r="D32" s="24" t="inlineStr"/>
+      <c r="E32" s="24" t="inlineStr"/>
+      <c r="F32" s="24" t="inlineStr"/>
+      <c r="G32" s="24" t="inlineStr"/>
+      <c r="H32" s="21" t="inlineStr">
+        <is>
+          <t>G | 460呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I32" s="21" t="inlineStr">
+        <is>
+          <t>H | 466呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J32" s="22" t="inlineStr">
+        <is>
+          <t>J | 549呎 (2房)
+$1516万
+$27,623/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="inlineStr">
+        <is>
+          <t>A | 639呎 (2房)
+$1761万
+$27,557/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C33" s="24" t="inlineStr"/>
+      <c r="D33" s="24" t="inlineStr"/>
+      <c r="E33" s="24" t="inlineStr"/>
+      <c r="F33" s="24" t="inlineStr"/>
+      <c r="G33" s="24" t="inlineStr"/>
+      <c r="H33" s="21" t="inlineStr">
+        <is>
+          <t>G | 460呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I33" s="21" t="inlineStr">
+        <is>
+          <t>H | 466呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J33" s="22" t="inlineStr">
+        <is>
+          <t>J | 549呎 (2房)
+$1494万
+$27,208/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-启德-维港．湾畔第1B期.xlsx
+++ b/files/九龙-启德-维港．湾畔第1B期.xlsx
@@ -662,7 +662,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/九龙-启德-维港．湾畔第1B期.xlsx
+++ b/files/九龙-启德-维港．湾畔第1B期.xlsx
@@ -35363,7 +35363,7 @@
           <t>A | 560呎 (2房)
 $1921万
 $34,307/呎
-(26年-06月-16日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -35371,7 +35371,7 @@
           <t>B | 516呎 (2房)
 $1742万
 $33,756/呎
-(26年-06月-10日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
@@ -35450,7 +35450,7 @@
           <t>B | 516呎 (2房)
 $1692万
 $32,791/呎
-(26年-06月-10日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr">
@@ -35521,7 +35521,7 @@
           <t>A | 560呎 (2房)
 $1848万
 $32,993/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -35529,7 +35529,7 @@
           <t>B | 516呎 (2房)
 $1675万
 $32,467/呎
-(26年-06月-23日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
@@ -35600,7 +35600,7 @@
           <t>A | 560呎 (2房)
 $1794万
 $32,030/呎
-(26年-04月-19日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -35608,7 +35608,7 @@
           <t>B | 516呎 (2房)
 $1627万
 $31,527/呎
-(26年-04月-19日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -35679,7 +35679,7 @@
           <t>A | 560呎 (2房)
 $1776万
 $31,714/呎
-(26年-05月-14日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -35687,7 +35687,7 @@
           <t>B | 516呎 (2房)
 $1611万
 $31,215/呎
-(26年-05月-07日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
@@ -35758,7 +35758,7 @@
           <t>A | 560呎 (2房)
 $1758万
 $31,400/呎
-(26年-04月-09日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -35766,7 +35766,7 @@
           <t>B | 516呎 (2房)
 $1595万
 $30,907/呎
-(26年-03月-24日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -35837,7 +35837,7 @@
           <t>A | 560呎 (2房)
 $1743万
 $31,130/呎
-(26年-02月-10日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -35845,7 +35845,7 @@
           <t>B | 516呎 (2房)
 $1548万
 $30,000/呎
-(26年-02月-04日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -35916,7 +35916,7 @@
           <t>A | 560呎 (2房)
 $1715万
 $30,627/呎
-(26年-02月-08日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -35924,7 +35924,7 @@
           <t>B | 516呎 (2房)
 $1540万
 $29,851/呎
-(26年-02月-05日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
@@ -35995,7 +35995,7 @@
           <t>A | 560呎 (2房)
 $1707万
 $30,475/呎
-(25年-09月-09日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -36003,7 +36003,7 @@
           <t>B | 516呎 (2房)
 $1533万
 $29,702/呎
-(25年-09月-16日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -36074,7 +36074,7 @@
           <t>A | 560呎 (2房)
 $1715万
 $30,627/呎
-(26年-03月-24日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -36082,7 +36082,7 @@
           <t>B | 516呎 (2房)
 $1525万
 $29,554/呎
-(26年-02月-23日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -36153,7 +36153,7 @@
           <t>A | 560呎 (2房)
 $1707万
 $30,475/呎
-(26年-03月-29日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -36161,7 +36161,7 @@
           <t>B | 516呎 (2房)
 $1517万
 $29,407/呎
-(25年-12月-08日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -36232,7 +36232,7 @@
           <t>A | 560呎 (2房)
 $1681万
 $30,023/呎
-(25年-09月-10日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -36240,7 +36240,7 @@
           <t>B | 516呎 (2房)
 $1510万
 $29,260/呎
-(25年-12月-22日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -36296,7 +36296,7 @@
           <t>J | 559呎 (2房)
 $1832万
 $32,771/呎
-(26年-06月-10日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -36311,7 +36311,7 @@
           <t>A | 560呎 (2房)
 $1673万
 $29,873/呎
-(25年-12月-03日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -36319,7 +36319,7 @@
           <t>B | 516呎 (2房)
 $1502万
 $29,114/呎
-(25年-11月-26日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -36375,7 +36375,7 @@
           <t>J | 559呎 (2房)
 $1823万
 $32,610/呎
-(26年-05月-17日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -36390,7 +36390,7 @@
           <t>A | 560呎 (2房)
 $1664万
 $29,723/呎
-(26年-01月-21日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -36398,7 +36398,7 @@
           <t>B | 516呎 (2房)
 $1495万
 $28,969/呎
-(25年-11月-18日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -36454,7 +36454,7 @@
           <t>J | 559呎 (2房)
 $1780万
 $31,844/呎
-(26年-05月-14日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -36469,7 +36469,7 @@
           <t>A | 560呎 (2房)
 $1694万
 $30,246/呎
-(25年-10月-23日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -36477,7 +36477,7 @@
           <t>B | 516呎 (2房)
 $1487万
 $28,826/呎
-(25年-11月-07日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -36533,7 +36533,7 @@
           <t>J | 559呎 (2房)
 $1805万
 $32,283/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -36627,7 +36627,7 @@
           <t>A | 560呎 (2房)
 $1631万
 $29,132/呎
-(25年-09月-09日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -36635,7 +36635,7 @@
           <t>B | 516呎 (2房)
 $1465万
 $28,393/呎
-(25年-09月-04日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -36691,7 +36691,7 @@
           <t>J | 559呎 (2房)
 $1734万
 $31,018/呎
-(26年-05月-04日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -36706,7 +36706,7 @@
           <t>A | 560呎 (2房)
 $1623万
 $28,988/呎
-(26年-01月-19日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -36714,7 +36714,7 @@
           <t>B | 516呎 (2房)
 $1458万
 $28,252/呎
-(25年-11月-03日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -36770,7 +36770,7 @@
           <t>J | 559呎 (2房)
 $1759万
 $31,460/呎
-(26年-04月-26日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -36785,7 +36785,7 @@
           <t>A | 560呎 (2房)
 $1615万
 $28,843/呎
-(25年-12月-07日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -36793,7 +36793,7 @@
           <t>B | 516呎 (2房)
 $1450万
 $28,110/呎
-(25年-09月-08日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
@@ -36849,7 +36849,7 @@
           <t>J | 559呎 (2房)
 $1711万
 $30,608/呎
-(26年-04月-26日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -36864,7 +36864,7 @@
           <t>A | 560呎 (2房)
 $1607万
 $28,698/呎
-(25年-12月-07日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -36872,7 +36872,7 @@
           <t>B | 516呎 (2房)
 $1443万
 $27,969/呎
-(25年-09月-17日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
@@ -36928,7 +36928,7 @@
           <t>J | 559呎 (2房)
 $1758万
 $31,444/呎
-(26年-04月-29日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -36943,7 +36943,7 @@
           <t>A | 560呎 (2房)
 $1599万
 $28,555/呎
-(26年-01月-21日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -36951,7 +36951,7 @@
           <t>B | 516呎 (2房)
 $1436万
 $27,829/呎
-(25年-11月-05日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -37007,7 +37007,7 @@
           <t>J | 559呎 (2房)
 $1710万
 $30,592/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -37022,7 +37022,7 @@
           <t>A | 560呎 (2房)
 $1591万
 $28,412/呎
-(26年-01月-19日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -37030,7 +37030,7 @@
           <t>B | 516呎 (2房)
 $1429万
 $27,692/呎
-(25年-09月-08日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="D27" s="21" t="inlineStr">
@@ -37086,7 +37086,7 @@
           <t>J | 559呎 (2房)
 $1702万
 $30,440/呎
-(26年-05月-05日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -37101,7 +37101,7 @@
           <t>A | 560呎 (2房)
 $1583万
 $28,270/呎
-(25年-11月-20日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -37109,7 +37109,7 @@
           <t>B | 516呎 (2房)
 $1422万
 $27,552/呎
-(25年-10月-12日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
@@ -37165,7 +37165,7 @@
           <t>J | 559呎 (2房)
 $1693万
 $30,288/呎
-(26年-04月-20日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -37180,7 +37180,7 @@
           <t>A | 560呎 (2房)
 $1559万
 $27,846/呎
-(25年-09月-14日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C29" s="22" t="inlineStr">
@@ -37188,7 +37188,7 @@
           <t>B | 516呎 (2房)
 $1400万
 $27,140/呎
-(25年-09月-01日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="D29" s="21" t="inlineStr">
@@ -37244,7 +37244,7 @@
           <t>J | 559呎 (2房)
 $1652万
 $29,551/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -37259,7 +37259,7 @@
           <t>A | 560呎 (2房)
 $1579万
 $28,195/呎
-(25年-09月-08日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C30" s="22" t="inlineStr">
@@ -37267,7 +37267,7 @@
           <t>B | 516呎 (2房)
 $1386万
 $26,868/呎
-(25年-09月-01日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="D30" s="21" t="inlineStr">
@@ -37323,7 +37323,7 @@
           <t>J | 559呎 (2房)
 $1620万
 $28,977/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -37338,7 +37338,7 @@
           <t>A | 560呎 (2房)
 $1528万
 $27,291/呎
-(25年-08月-14日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C31" s="22" t="inlineStr">
@@ -37346,7 +37346,7 @@
           <t>B | 516呎 (2房)
 $1372万
 $26,599/呎
-(25年-09月-14日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="D31" s="21" t="inlineStr">
@@ -37402,7 +37402,7 @@
           <t>J | 559呎 (2房)
 $1619万
 $28,962/呎
-(26年-04月-29日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -37417,7 +37417,7 @@
           <t>A | 560呎 (2房)
 $1540万
 $27,493/呎
-(25年-12月-15日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="C32" s="22" t="inlineStr">
@@ -37425,7 +37425,7 @@
           <t>B | 516呎 (2房)
 $1352万
 $26,200/呎
-(25年-09月-01日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="D32" s="21" t="inlineStr">
@@ -37481,7 +37481,7 @@
           <t>J | 559呎 (2房)
 $1580万
 $28,258/呎
-(26年-04月-14日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -37496,7 +37496,7 @@
           <t>A | 560呎 (2房)
 $1483万
 $26,488/呎
-(25年-12月-04日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="C33" s="22" t="inlineStr">
@@ -37504,7 +37504,7 @@
           <t>B | 516呎 (2房)
 $1333万
 $25,828/呎
-(25年-10月-12日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="D33" s="21" t="inlineStr">
@@ -37560,7 +37560,7 @@
           <t>J | 559呎 (2房)
 $1586万
 $28,369/呎
-(26年-05月-18日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -37728,7 +37728,7 @@
           <t>A | 670呎 (3房)
 $2424万
 $36,187/呎
-(26年-04月-12日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr">
@@ -37744,7 +37744,7 @@
           <t>C | 568呎 (3房)
 $2117万
 $37,276/呎
-(26年-06月-11日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr">
@@ -37807,7 +37807,7 @@
           <t>A | 670呎 (3房)
 $2320万
 $34,634/呎
-(26年-03月-02日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -37815,7 +37815,7 @@
           <t>B | 579呎 (2房)
 $2047万
 $35,361/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -37823,7 +37823,7 @@
           <t>C | 568呎 (3房)
 $1993万
 $35,086/呎
-(26年-03月-02日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr">
@@ -37886,7 +37886,7 @@
           <t>A | 670呎 (3房)
 $2298万
 $34,291/呎
-(26年-02月-12日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -37894,7 +37894,7 @@
           <t>B | 579呎 (2房)
 $1956万
 $33,777/呎
-(26年-01月-19日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -37902,7 +37902,7 @@
           <t>C | 568呎 (3房)
 $2050万
 $36,088/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E7" s="21" t="inlineStr">
@@ -37950,7 +37950,7 @@
           <t>J | 549呎 (2房)
 $1825万
 $33,242/呎
-(26年-03月-09日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -37965,7 +37965,7 @@
           <t>A | 670呎 (3房)
 $2275万
 $33,952/呎
-(26年-02月-03日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -37973,7 +37973,7 @@
           <t>B | 579呎 (2房)
 $1931万
 $33,356/呎
-(26年-02月-08日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -37981,7 +37981,7 @@
           <t>C | 568呎 (3房)
 $2086万
 $36,732/呎
-(26年-07月-06日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E8" s="21" t="inlineStr">
@@ -38044,7 +38044,7 @@
           <t>A | 670呎 (3房)
 $2252万
 $33,613/呎
-(26年-01月-08日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -38052,7 +38052,7 @@
           <t>B | 579呎 (2房)
 $1912万
 $33,026/呎
-(26年-02月-03日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -38060,7 +38060,7 @@
           <t>C | 568呎 (3房)
 $1972万
 $34,715/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E9" s="21" t="inlineStr">
@@ -38108,7 +38108,7 @@
           <t>J | 549呎 (2房)
 $1878万
 $34,217/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -38123,7 +38123,7 @@
           <t>A | 670呎 (3房)
 $2230万
 $33,282/呎
-(25年-12月-23日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -38131,7 +38131,7 @@
           <t>B | 579呎 (2房)
 $1968万
 $33,981/呎
-(26年-05月-17日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -38139,7 +38139,7 @@
           <t>C | 568呎 (3房)
 $1952万
 $34,371/呎
-(26年-05月-11日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E10" s="21" t="inlineStr">
@@ -38202,7 +38202,7 @@
           <t>A | 670呎 (3房)
 $2186万
 $32,630/呎
-(25年-12月-04日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -38210,7 +38210,7 @@
           <t>B | 579呎 (2房)
 $1948万
 $33,644/呎
-(26年-05月-14日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -38218,7 +38218,7 @@
           <t>C | 568呎 (3房)
 $1915万
 $33,708/呎
-(26年-04月-09日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E11" s="21" t="inlineStr">
@@ -38266,7 +38266,7 @@
           <t>J | 549呎 (2房)
 $1789万
 $32,583/呎
-(26年-04月-14日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -38281,7 +38281,7 @@
           <t>A | 669呎 (3房)
 $2143万
 $32,033/呎
-(25年-10月-02日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -38289,7 +38289,7 @@
           <t>B | 579呎 (2房)
 $1856万
 $32,054/呎
-(26年-02月-12日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -38297,7 +38297,7 @@
           <t>C | 568呎 (3房)
 $1859万
 $32,732/呎
-(26年-01月-21日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="E12" s="21" t="inlineStr">
@@ -38345,7 +38345,7 @@
           <t>J | 549呎 (2房)
 $1791万
 $32,630/呎
-(26年-04月-19日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -38360,7 +38360,7 @@
           <t>A | 669呎 (3房)
 $2132万
 $31,874/呎
-(25年-09月-11日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -38368,7 +38368,7 @@
           <t>B | 579呎 (2房)
 $1831万
 $31,623/呎
-(26年-01月-05日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -38376,7 +38376,7 @@
           <t>C | 568呎 (3房)
 $1814万
 $31,930/呎
-(26年-01月-15日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr">
@@ -38439,7 +38439,7 @@
           <t>A | 670呎 (3房)
 $2192万
 $32,713/呎
-(25年-10月-19日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -38447,7 +38447,7 @@
           <t>B | 579呎 (2房)
 $1802万
 $31,114/呎
-(26年-01月-06日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -38455,7 +38455,7 @@
           <t>C | 568呎 (3房)
 $1841万
 $32,407/呎
-(26年-02月-12日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr">
@@ -38503,7 +38503,7 @@
           <t>J | 549呎 (2房)
 $1805万
 $32,880/呎
-(26年-05月-12日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -38518,7 +38518,7 @@
           <t>A | 670呎 (3房)
 $2174万
 $32,455/呎
-(25年-10月-21日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -38526,7 +38526,7 @@
           <t>B | 579呎 (2房)
 $1792万
 $30,959/呎
-(25年-09月-25日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -38534,7 +38534,7 @@
           <t>C | 568呎 (3房)
 $1868万
 $32,879/呎
-(26年-03月-15日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr">
@@ -38582,7 +38582,7 @@
           <t>J | 549呎 (2房)
 $1745万
 $31,783/呎
-(26年-04月-29日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -38597,7 +38597,7 @@
           <t>A | 669呎 (3房)
 $2101万
 $31,401/呎
-(25年-10月-02日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -38605,7 +38605,7 @@
           <t>B | 579呎 (2房)
 $1784万
 $30,805/呎
-(25年-09月-11日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -38613,7 +38613,7 @@
           <t>C | 568呎 (3房)
 $1822万
 $32,086/呎
-(26年-02月-09日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr">
@@ -38661,7 +38661,7 @@
           <t>J | 549呎 (2房)
 $1736万
 $31,625/呎
-(26年-04月-26日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -38676,7 +38676,7 @@
           <t>A | 669呎 (3房)
 $2090万
 $31,245/呎
-(25年-09月-10日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -38684,7 +38684,7 @@
           <t>B | 579呎 (2房)
 $1775万
 $30,651/呎
-(25年-10月-12日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -38692,7 +38692,7 @@
           <t>C | 569呎 (3房)
 $1778万
 $31,244/呎
-(25年-09月-10日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr">
@@ -38740,7 +38740,7 @@
           <t>J | 549呎 (2房)
 $1728万
 $31,466/呎
-(26年-04月-13日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -38755,7 +38755,7 @@
           <t>A | 669呎 (3房)
 $2104万
 $31,444/呎
-(25年-09月-15日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -38763,7 +38763,7 @@
           <t>B | 579呎 (2房)
 $1766万
 $30,499/呎
-(25年-09月-10日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -38771,7 +38771,7 @@
           <t>C | 568呎 (3房)
 $1769万
 $31,144/呎
-(25年-12月-10日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr">
@@ -38819,7 +38819,7 @@
           <t>J | 549呎 (2房)
 $1719万
 $31,311/呎
-(26年-04月-01日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -38834,7 +38834,7 @@
           <t>A | 669呎 (3房)
 $2070万
 $30,934/呎
-(25年-09月-28日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -38842,7 +38842,7 @@
           <t>B | 579呎 (2房)
 $1757万
 $30,347/呎
-(25年-11月-08日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -38850,7 +38850,7 @@
           <t>C | 568呎 (3房)
 $1760万
 $30,988/呎
-(25年-12月-18日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
@@ -38898,7 +38898,7 @@
           <t>J | 549呎 (2房)
 $1694万
 $30,849/呎
-(26年-03月-10日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -38913,7 +38913,7 @@
           <t>A | 670呎 (3房)
 $2082万
 $31,082/呎
-(25年-09月-18日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -38921,7 +38921,7 @@
           <t>B | 579呎 (2房)
 $1748万
 $30,195/呎
-(25年-10月-02日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -38929,7 +38929,7 @@
           <t>C | 568呎 (3房)
 $1791万
 $31,533/呎
-(25年-09月-10日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr">
@@ -38977,7 +38977,7 @@
           <t>J | 549呎 (2房)
 $1685万
 $30,694/呎
-(26年-03月-22日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -39071,7 +39071,7 @@
           <t>A | 669呎 (3房)
 $2028万
 $30,318/呎
-(25年-09月-10日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -39079,7 +39079,7 @@
           <t>B | 579呎 (2房)
 $1722万
 $29,743/呎
-(25年-09月-11日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -39087,7 +39087,7 @@
           <t>C | 569呎 (3房)
 $1725万
 $30,318/呎
-(25年-09月-10日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
@@ -39135,7 +39135,7 @@
           <t>J | 549呎 (2房)
 $1676万
 $30,534/呎
-(26年-04月-01日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -39150,7 +39150,7 @@
           <t>A | 669呎 (3房)
 $2018万
 $30,167/呎
-(25年-09月-16日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -39158,7 +39158,7 @@
           <t>B | 579呎 (2房)
 $1714万
 $29,594/呎
-(25年-09月-24日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -39166,7 +39166,7 @@
           <t>C | 568呎 (3房)
 $1716万
 $30,220/呎
-(25年-11月-24日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
@@ -39214,7 +39214,7 @@
           <t>J | 549呎 (2房)
 $1668万
 $30,383/呎
-(26年-03月-26日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -39229,7 +39229,7 @@
           <t>A | 669呎 (3房)
 $2008万
 $30,016/呎
-(25年-09月-10日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -39237,7 +39237,7 @@
           <t>B | 579呎 (2房)
 $1724万
 $29,781/呎
-(25年-09月-15日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -39245,7 +39245,7 @@
           <t>C | 568呎 (3房)
 $1708万
 $30,069/呎
-(26年-01月-18日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
@@ -39293,7 +39293,7 @@
           <t>J | 549呎 (2房)
 $1681万
 $30,614/呎
-(26年-03月-18日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -39308,7 +39308,7 @@
           <t>A | 669呎 (3房)
 $1998万
 $29,867/呎
-(25年-10月-02日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -39316,7 +39316,7 @@
           <t>B | 579呎 (2房)
 $1696万
 $29,299/呎
-(25年-09月-10日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -39324,7 +39324,7 @@
           <t>C | 569呎 (3房)
 $1699万
 $29,866/呎
-(25年-11月-17日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr">
@@ -39372,7 +39372,7 @@
           <t>J | 549呎 (2房)
 $1635万
 $29,783/呎
-(26年-03月-17日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -39387,7 +39387,7 @@
           <t>A | 670呎 (3房)
 $2048万
 $30,564/呎
-(25年-10月-27日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -39395,7 +39395,7 @@
           <t>B | 579呎 (2房)
 $1688万
 $29,152/呎
-(25年-10月-30日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -39403,7 +39403,7 @@
           <t>C | 569呎 (3房)
 $1729万
 $30,392/呎
-(26年-01月-11日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="E26" s="21" t="inlineStr">
@@ -39451,7 +39451,7 @@
           <t>J | 549呎 (2房)
 $1611万
 $29,341/呎
-(26年-03月-19日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -39466,7 +39466,7 @@
           <t>A | 669呎 (3房)
 $1978万
 $29,568/呎
-(25年-09月-22日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -39474,7 +39474,7 @@
           <t>B | 579呎 (2房)
 $1680万
 $29,007/呎
-(25年-10月-22日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -39482,7 +39482,7 @@
           <t>C | 568呎 (3房)
 $1682万
 $29,620/呎
-(26年-01月-11日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr">
@@ -39530,7 +39530,7 @@
           <t>J | 549呎 (2房)
 $1603万
 $29,195/呎
-(26年-02月-26日)</t>
+(26年-02月)</t>
         </is>
       </c>
     </row>
@@ -39545,7 +39545,7 @@
           <t>A | 669呎 (3房)
 $1968万
 $29,420/呎
-(25年-09月-25日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -39553,7 +39553,7 @@
           <t>B | 579呎 (2房)
 $1671万
 $28,862/呎
-(25年-10月-22日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -39561,7 +39561,7 @@
           <t>C | 568呎 (3房)
 $1674万
 $29,472/呎
-(25年-10月-23日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="E28" s="21" t="inlineStr">
@@ -39609,7 +39609,7 @@
           <t>J | 549呎 (2房)
 $1611万
 $29,339/呎
-(26年-03月-22日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -39624,7 +39624,7 @@
           <t>A | 669呎 (3房)
 $1958万
 $29,269/呎
-(25年-10月-02日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C29" s="22" t="inlineStr">
@@ -39632,7 +39632,7 @@
           <t>B | 579呎 (2房)
 $1646万
 $28,428/呎
-(25年-11月-30日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -39640,7 +39640,7 @@
           <t>C | 568呎 (3房)
 $1649万
 $29,030/呎
-(25年-12月-02日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="E29" s="21" t="inlineStr">
@@ -39688,7 +39688,7 @@
           <t>J | 549呎 (2房)
 $1571万
 $28,612/呎
-(26年-02月-26日)</t>
+(26年-02月)</t>
         </is>
       </c>
     </row>
@@ -39703,7 +39703,7 @@
           <t>A | 670呎 (3房)
 $1941万
 $28,972/呎
-(25年-10月-02日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C30" s="22" t="inlineStr">
@@ -39711,7 +39711,7 @@
           <t>B | 579呎 (2房)
 $1630万
 $28,145/呎
-(25年-10月-12日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
@@ -39719,7 +39719,7 @@
           <t>C | 568呎 (3房)
 $1632万
 $28,739/呎
-(25年-09月-17日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="E30" s="21" t="inlineStr">
@@ -39767,7 +39767,7 @@
           <t>J | 549呎 (2房)
 $1573万
 $28,648/呎
-(26年-03月-01日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -39782,7 +39782,7 @@
           <t>A | 670呎 (3房)
 $1902万
 $28,385/呎
-(25年-10月-21日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C31" s="22" t="inlineStr">
@@ -39790,7 +39790,7 @@
           <t>B | 579呎 (2房)
 $1650万
 $28,496/呎
-(25年-12月-07日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -39798,7 +39798,7 @@
           <t>C | 568呎 (3房)
 $1617万
 $28,468/呎
-(25年-12月-09日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="E31" s="21" t="inlineStr">
@@ -39839,7 +39839,7 @@
           <t>J | 549呎 (2房)
 $1555万
 $28,324/呎
-(26年-03月-12日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -39854,7 +39854,7 @@
           <t>A | 639呎 (2房)
 $1788万
 $27,977/呎
-(25年-11月-04日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C32" s="24" t="inlineStr"/>
@@ -39883,7 +39883,7 @@
           <t>J | 549呎 (2房)
 $1516万
 $27,623/呎
-(26年-02月-11日)</t>
+(26年-02月)</t>
         </is>
       </c>
     </row>
@@ -39898,7 +39898,7 @@
           <t>A | 639呎 (2房)
 $1761万
 $27,557/呎
-(25年-10月-01日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C33" s="24" t="inlineStr"/>
@@ -39927,7 +39927,7 @@
           <t>J | 549呎 (2房)
 $1494万
 $27,208/呎
-(26年-03月-01日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-启德-维港．湾畔第1B期.xlsx
+++ b/files/九龙-启德-维港．湾畔第1B期.xlsx
@@ -35363,7 +35363,7 @@
           <t>A | 560呎 (2房)
 $1921万
 $34,307/呎
-(26年-06月)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -35371,7 +35371,7 @@
           <t>B | 516呎 (2房)
 $1742万
 $33,756/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
@@ -35450,7 +35450,7 @@
           <t>B | 516呎 (2房)
 $1692万
 $32,791/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr">
@@ -35521,7 +35521,7 @@
           <t>A | 560呎 (2房)
 $1848万
 $32,993/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -35529,7 +35529,7 @@
           <t>B | 516呎 (2房)
 $1675万
 $32,467/呎
-(26年-06月)</t>
+(26年-06月-23日)</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
@@ -35600,7 +35600,7 @@
           <t>A | 560呎 (2房)
 $1794万
 $32,030/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -35608,7 +35608,7 @@
           <t>B | 516呎 (2房)
 $1627万
 $31,527/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -35679,7 +35679,7 @@
           <t>A | 560呎 (2房)
 $1776万
 $31,714/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -35687,7 +35687,7 @@
           <t>B | 516呎 (2房)
 $1611万
 $31,215/呎
-(26年-05月)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
@@ -35758,7 +35758,7 @@
           <t>A | 560呎 (2房)
 $1758万
 $31,400/呎
-(26年-04月)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -35766,7 +35766,7 @@
           <t>B | 516呎 (2房)
 $1595万
 $30,907/呎
-(26年-03月)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -35837,7 +35837,7 @@
           <t>A | 560呎 (2房)
 $1743万
 $31,130/呎
-(26年-02月)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -35845,7 +35845,7 @@
           <t>B | 516呎 (2房)
 $1548万
 $30,000/呎
-(26年-02月)</t>
+(26年-02月-04日)</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -35916,7 +35916,7 @@
           <t>A | 560呎 (2房)
 $1715万
 $30,627/呎
-(26年-02月)</t>
+(26年-02月-08日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -35924,7 +35924,7 @@
           <t>B | 516呎 (2房)
 $1540万
 $29,851/呎
-(26年-02月)</t>
+(26年-02月-05日)</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
@@ -35995,7 +35995,7 @@
           <t>A | 560呎 (2房)
 $1707万
 $30,475/呎
-(25年-09月)</t>
+(25年-09月-09日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -36003,7 +36003,7 @@
           <t>B | 516呎 (2房)
 $1533万
 $29,702/呎
-(25年-09月)</t>
+(25年-09月-16日)</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -36074,7 +36074,7 @@
           <t>A | 560呎 (2房)
 $1715万
 $30,627/呎
-(26年-03月)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -36082,7 +36082,7 @@
           <t>B | 516呎 (2房)
 $1525万
 $29,554/呎
-(26年-02月)</t>
+(26年-02月-23日)</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -36153,7 +36153,7 @@
           <t>A | 560呎 (2房)
 $1707万
 $30,475/呎
-(26年-03月)</t>
+(26年-03月-29日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -36161,7 +36161,7 @@
           <t>B | 516呎 (2房)
 $1517万
 $29,407/呎
-(25年-12月)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -36232,7 +36232,7 @@
           <t>A | 560呎 (2房)
 $1681万
 $30,023/呎
-(25年-09月)</t>
+(25年-09月-10日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -36240,7 +36240,7 @@
           <t>B | 516呎 (2房)
 $1510万
 $29,260/呎
-(25年-12月)</t>
+(25年-12月-22日)</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -36296,7 +36296,7 @@
           <t>J | 559呎 (2房)
 $1832万
 $32,771/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
     </row>
@@ -36311,7 +36311,7 @@
           <t>A | 560呎 (2房)
 $1673万
 $29,873/呎
-(25年-12月)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -36319,7 +36319,7 @@
           <t>B | 516呎 (2房)
 $1502万
 $29,114/呎
-(25年-11月)</t>
+(25年-11月-26日)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -36375,7 +36375,7 @@
           <t>J | 559呎 (2房)
 $1823万
 $32,610/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
     </row>
@@ -36390,7 +36390,7 @@
           <t>A | 560呎 (2房)
 $1664万
 $29,723/呎
-(26年-01月)</t>
+(26年-01月-21日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -36398,7 +36398,7 @@
           <t>B | 516呎 (2房)
 $1495万
 $28,969/呎
-(25年-11月)</t>
+(25年-11月-18日)</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -36454,7 +36454,7 @@
           <t>J | 559呎 (2房)
 $1780万
 $31,844/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
     </row>
@@ -36469,7 +36469,7 @@
           <t>A | 560呎 (2房)
 $1694万
 $30,246/呎
-(25年-10月)</t>
+(25年-10月-23日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -36477,7 +36477,7 @@
           <t>B | 516呎 (2房)
 $1487万
 $28,826/呎
-(25年-11月)</t>
+(25年-11月-07日)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -36533,7 +36533,7 @@
           <t>J | 559呎 (2房)
 $1805万
 $32,283/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
     </row>
@@ -36627,7 +36627,7 @@
           <t>A | 560呎 (2房)
 $1631万
 $29,132/呎
-(25年-09月)</t>
+(25年-09月-09日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -36635,7 +36635,7 @@
           <t>B | 516呎 (2房)
 $1465万
 $28,393/呎
-(25年-09月)</t>
+(25年-09月-04日)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -36691,7 +36691,7 @@
           <t>J | 559呎 (2房)
 $1734万
 $31,018/呎
-(26年-05月)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
     </row>
@@ -36706,7 +36706,7 @@
           <t>A | 560呎 (2房)
 $1623万
 $28,988/呎
-(26年-01月)</t>
+(26年-01月-19日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -36714,7 +36714,7 @@
           <t>B | 516呎 (2房)
 $1458万
 $28,252/呎
-(25年-11月)</t>
+(25年-11月-03日)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -36770,7 +36770,7 @@
           <t>J | 559呎 (2房)
 $1759万
 $31,460/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
     </row>
@@ -36785,7 +36785,7 @@
           <t>A | 560呎 (2房)
 $1615万
 $28,843/呎
-(25年-12月)</t>
+(25年-12月-07日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -36793,7 +36793,7 @@
           <t>B | 516呎 (2房)
 $1450万
 $28,110/呎
-(25年-09月)</t>
+(25年-09月-08日)</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
@@ -36849,7 +36849,7 @@
           <t>J | 559呎 (2房)
 $1711万
 $30,608/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
     </row>
@@ -36864,7 +36864,7 @@
           <t>A | 560呎 (2房)
 $1607万
 $28,698/呎
-(25年-12月)</t>
+(25年-12月-07日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -36872,7 +36872,7 @@
           <t>B | 516呎 (2房)
 $1443万
 $27,969/呎
-(25年-09月)</t>
+(25年-09月-17日)</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
@@ -36928,7 +36928,7 @@
           <t>J | 559呎 (2房)
 $1758万
 $31,444/呎
-(26年-04月)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
     </row>
@@ -36943,7 +36943,7 @@
           <t>A | 560呎 (2房)
 $1599万
 $28,555/呎
-(26年-01月)</t>
+(26年-01月-21日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -36951,7 +36951,7 @@
           <t>B | 516呎 (2房)
 $1436万
 $27,829/呎
-(25年-11月)</t>
+(25年-11月-05日)</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -37007,7 +37007,7 @@
           <t>J | 559呎 (2房)
 $1710万
 $30,592/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
     </row>
@@ -37022,7 +37022,7 @@
           <t>A | 560呎 (2房)
 $1591万
 $28,412/呎
-(26年-01月)</t>
+(26年-01月-19日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -37030,7 +37030,7 @@
           <t>B | 516呎 (2房)
 $1429万
 $27,692/呎
-(25年-09月)</t>
+(25年-09月-08日)</t>
         </is>
       </c>
       <c r="D27" s="21" t="inlineStr">
@@ -37086,7 +37086,7 @@
           <t>J | 559呎 (2房)
 $1702万
 $30,440/呎
-(26年-05月)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
     </row>
@@ -37101,7 +37101,7 @@
           <t>A | 560呎 (2房)
 $1583万
 $28,270/呎
-(25年-11月)</t>
+(25年-11月-20日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -37109,7 +37109,7 @@
           <t>B | 516呎 (2房)
 $1422万
 $27,552/呎
-(25年-10月)</t>
+(25年-10月-12日)</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
@@ -37165,7 +37165,7 @@
           <t>J | 559呎 (2房)
 $1693万
 $30,288/呎
-(26年-04月)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
     </row>
@@ -37180,7 +37180,7 @@
           <t>A | 560呎 (2房)
 $1559万
 $27,846/呎
-(25年-09月)</t>
+(25年-09月-14日)</t>
         </is>
       </c>
       <c r="C29" s="22" t="inlineStr">
@@ -37188,7 +37188,7 @@
           <t>B | 516呎 (2房)
 $1400万
 $27,140/呎
-(25年-09月)</t>
+(25年-09月-01日)</t>
         </is>
       </c>
       <c r="D29" s="21" t="inlineStr">
@@ -37244,7 +37244,7 @@
           <t>J | 559呎 (2房)
 $1652万
 $29,551/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
     </row>
@@ -37259,7 +37259,7 @@
           <t>A | 560呎 (2房)
 $1579万
 $28,195/呎
-(25年-09月)</t>
+(25年-09月-08日)</t>
         </is>
       </c>
       <c r="C30" s="22" t="inlineStr">
@@ -37267,7 +37267,7 @@
           <t>B | 516呎 (2房)
 $1386万
 $26,868/呎
-(25年-09月)</t>
+(25年-09月-01日)</t>
         </is>
       </c>
       <c r="D30" s="21" t="inlineStr">
@@ -37323,7 +37323,7 @@
           <t>J | 559呎 (2房)
 $1620万
 $28,977/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
     </row>
@@ -37338,7 +37338,7 @@
           <t>A | 560呎 (2房)
 $1528万
 $27,291/呎
-(25年-08月)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
       <c r="C31" s="22" t="inlineStr">
@@ -37346,7 +37346,7 @@
           <t>B | 516呎 (2房)
 $1372万
 $26,599/呎
-(25年-09月)</t>
+(25年-09月-14日)</t>
         </is>
       </c>
       <c r="D31" s="21" t="inlineStr">
@@ -37402,7 +37402,7 @@
           <t>J | 559呎 (2房)
 $1619万
 $28,962/呎
-(26年-04月)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
     </row>
@@ -37417,7 +37417,7 @@
           <t>A | 560呎 (2房)
 $1540万
 $27,493/呎
-(25年-12月)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
       <c r="C32" s="22" t="inlineStr">
@@ -37425,7 +37425,7 @@
           <t>B | 516呎 (2房)
 $1352万
 $26,200/呎
-(25年-09月)</t>
+(25年-09月-01日)</t>
         </is>
       </c>
       <c r="D32" s="21" t="inlineStr">
@@ -37481,7 +37481,7 @@
           <t>J | 559呎 (2房)
 $1580万
 $28,258/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
     </row>
@@ -37496,7 +37496,7 @@
           <t>A | 560呎 (2房)
 $1483万
 $26,488/呎
-(25年-12月)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="C33" s="22" t="inlineStr">
@@ -37504,7 +37504,7 @@
           <t>B | 516呎 (2房)
 $1333万
 $25,828/呎
-(25年-10月)</t>
+(25年-10月-12日)</t>
         </is>
       </c>
       <c r="D33" s="21" t="inlineStr">
@@ -37560,7 +37560,7 @@
           <t>J | 559呎 (2房)
 $1586万
 $28,369/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
     </row>
@@ -37728,7 +37728,7 @@
           <t>A | 670呎 (3房)
 $2424万
 $36,187/呎
-(26年-04月)</t>
+(26年-04月-12日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr">
@@ -37744,7 +37744,7 @@
           <t>C | 568呎 (3房)
 $2117万
 $37,276/呎
-(26年-06月)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr">
@@ -37807,7 +37807,7 @@
           <t>A | 670呎 (3房)
 $2320万
 $34,634/呎
-(26年-03月)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -37815,7 +37815,7 @@
           <t>B | 579呎 (2房)
 $2047万
 $35,361/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -37823,7 +37823,7 @@
           <t>C | 568呎 (3房)
 $1993万
 $35,086/呎
-(26年-03月)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr">
@@ -37886,7 +37886,7 @@
           <t>A | 670呎 (3房)
 $2298万
 $34,291/呎
-(26年-02月)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -37894,7 +37894,7 @@
           <t>B | 579呎 (2房)
 $1956万
 $33,777/呎
-(26年-01月)</t>
+(26年-01月-19日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -37902,7 +37902,7 @@
           <t>C | 568呎 (3房)
 $2050万
 $36,088/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="E7" s="21" t="inlineStr">
@@ -37950,7 +37950,7 @@
           <t>J | 549呎 (2房)
 $1825万
 $33,242/呎
-(26年-03月)</t>
+(26年-03月-09日)</t>
         </is>
       </c>
     </row>
@@ -37965,7 +37965,7 @@
           <t>A | 670呎 (3房)
 $2275万
 $33,952/呎
-(26年-02月)</t>
+(26年-02月-03日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -37973,7 +37973,7 @@
           <t>B | 579呎 (2房)
 $1931万
 $33,356/呎
-(26年-02月)</t>
+(26年-02月-08日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -37981,7 +37981,7 @@
           <t>C | 568呎 (3房)
 $2086万
 $36,732/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="E8" s="21" t="inlineStr">
@@ -38044,7 +38044,7 @@
           <t>A | 670呎 (3房)
 $2252万
 $33,613/呎
-(26年-01月)</t>
+(26年-01月-08日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -38052,7 +38052,7 @@
           <t>B | 579呎 (2房)
 $1912万
 $33,026/呎
-(26年-02月)</t>
+(26年-02月-03日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -38060,7 +38060,7 @@
           <t>C | 568呎 (3房)
 $1972万
 $34,715/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="E9" s="21" t="inlineStr">
@@ -38108,7 +38108,7 @@
           <t>J | 549呎 (2房)
 $1878万
 $34,217/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
     </row>
@@ -38123,7 +38123,7 @@
           <t>A | 670呎 (3房)
 $2230万
 $33,282/呎
-(25年-12月)</t>
+(25年-12月-23日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -38131,7 +38131,7 @@
           <t>B | 579呎 (2房)
 $1968万
 $33,981/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -38139,7 +38139,7 @@
           <t>C | 568呎 (3房)
 $1952万
 $34,371/呎
-(26年-05月)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="E10" s="21" t="inlineStr">
@@ -38202,7 +38202,7 @@
           <t>A | 670呎 (3房)
 $2186万
 $32,630/呎
-(25年-12月)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -38210,7 +38210,7 @@
           <t>B | 579呎 (2房)
 $1948万
 $33,644/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -38218,7 +38218,7 @@
           <t>C | 568呎 (3房)
 $1915万
 $33,708/呎
-(26年-04月)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="E11" s="21" t="inlineStr">
@@ -38266,7 +38266,7 @@
           <t>J | 549呎 (2房)
 $1789万
 $32,583/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
     </row>
@@ -38281,7 +38281,7 @@
           <t>A | 669呎 (3房)
 $2143万
 $32,033/呎
-(25年-10月)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -38289,7 +38289,7 @@
           <t>B | 579呎 (2房)
 $1856万
 $32,054/呎
-(26年-02月)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -38297,7 +38297,7 @@
           <t>C | 568呎 (3房)
 $1859万
 $32,732/呎
-(26年-01月)</t>
+(26年-01月-21日)</t>
         </is>
       </c>
       <c r="E12" s="21" t="inlineStr">
@@ -38345,7 +38345,7 @@
           <t>J | 549呎 (2房)
 $1791万
 $32,630/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
     </row>
@@ -38360,7 +38360,7 @@
           <t>A | 669呎 (3房)
 $2132万
 $31,874/呎
-(25年-09月)</t>
+(25年-09月-11日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -38368,7 +38368,7 @@
           <t>B | 579呎 (2房)
 $1831万
 $31,623/呎
-(26年-01月)</t>
+(26年-01月-05日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -38376,7 +38376,7 @@
           <t>C | 568呎 (3房)
 $1814万
 $31,930/呎
-(26年-01月)</t>
+(26年-01月-15日)</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr">
@@ -38439,7 +38439,7 @@
           <t>A | 670呎 (3房)
 $2192万
 $32,713/呎
-(25年-10月)</t>
+(25年-10月-19日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -38447,7 +38447,7 @@
           <t>B | 579呎 (2房)
 $1802万
 $31,114/呎
-(26年-01月)</t>
+(26年-01月-06日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -38455,7 +38455,7 @@
           <t>C | 568呎 (3房)
 $1841万
 $32,407/呎
-(26年-02月)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr">
@@ -38503,7 +38503,7 @@
           <t>J | 549呎 (2房)
 $1805万
 $32,880/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
     </row>
@@ -38518,7 +38518,7 @@
           <t>A | 670呎 (3房)
 $2174万
 $32,455/呎
-(25年-10月)</t>
+(25年-10月-21日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -38526,7 +38526,7 @@
           <t>B | 579呎 (2房)
 $1792万
 $30,959/呎
-(25年-09月)</t>
+(25年-09月-25日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -38534,7 +38534,7 @@
           <t>C | 568呎 (3房)
 $1868万
 $32,879/呎
-(26年-03月)</t>
+(26年-03月-15日)</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr">
@@ -38582,7 +38582,7 @@
           <t>J | 549呎 (2房)
 $1745万
 $31,783/呎
-(26年-04月)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
     </row>
@@ -38597,7 +38597,7 @@
           <t>A | 669呎 (3房)
 $2101万
 $31,401/呎
-(25年-10月)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -38605,7 +38605,7 @@
           <t>B | 579呎 (2房)
 $1784万
 $30,805/呎
-(25年-09月)</t>
+(25年-09月-11日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -38613,7 +38613,7 @@
           <t>C | 568呎 (3房)
 $1822万
 $32,086/呎
-(26年-02月)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr">
@@ -38661,7 +38661,7 @@
           <t>J | 549呎 (2房)
 $1736万
 $31,625/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
     </row>
@@ -38676,7 +38676,7 @@
           <t>A | 669呎 (3房)
 $2090万
 $31,245/呎
-(25年-09月)</t>
+(25年-09月-10日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -38684,7 +38684,7 @@
           <t>B | 579呎 (2房)
 $1775万
 $30,651/呎
-(25年-10月)</t>
+(25年-10月-12日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -38692,7 +38692,7 @@
           <t>C | 569呎 (3房)
 $1778万
 $31,244/呎
-(25年-09月)</t>
+(25年-09月-10日)</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr">
@@ -38740,7 +38740,7 @@
           <t>J | 549呎 (2房)
 $1728万
 $31,466/呎
-(26年-04月)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
     </row>
@@ -38755,7 +38755,7 @@
           <t>A | 669呎 (3房)
 $2104万
 $31,444/呎
-(25年-09月)</t>
+(25年-09月-15日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -38763,7 +38763,7 @@
           <t>B | 579呎 (2房)
 $1766万
 $30,499/呎
-(25年-09月)</t>
+(25年-09月-10日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -38771,7 +38771,7 @@
           <t>C | 568呎 (3房)
 $1769万
 $31,144/呎
-(25年-12月)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr">
@@ -38819,7 +38819,7 @@
           <t>J | 549呎 (2房)
 $1719万
 $31,311/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
     </row>
@@ -38834,7 +38834,7 @@
           <t>A | 669呎 (3房)
 $2070万
 $30,934/呎
-(25年-09月)</t>
+(25年-09月-28日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -38842,7 +38842,7 @@
           <t>B | 579呎 (2房)
 $1757万
 $30,347/呎
-(25年-11月)</t>
+(25年-11月-08日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -38850,7 +38850,7 @@
           <t>C | 568呎 (3房)
 $1760万
 $30,988/呎
-(25年-12月)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
@@ -38898,7 +38898,7 @@
           <t>J | 549呎 (2房)
 $1694万
 $30,849/呎
-(26年-03月)</t>
+(26年-03月-10日)</t>
         </is>
       </c>
     </row>
@@ -38913,7 +38913,7 @@
           <t>A | 670呎 (3房)
 $2082万
 $31,082/呎
-(25年-09月)</t>
+(25年-09月-18日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -38921,7 +38921,7 @@
           <t>B | 579呎 (2房)
 $1748万
 $30,195/呎
-(25年-10月)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -38929,7 +38929,7 @@
           <t>C | 568呎 (3房)
 $1791万
 $31,533/呎
-(25年-09月)</t>
+(25年-09月-10日)</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr">
@@ -38977,7 +38977,7 @@
           <t>J | 549呎 (2房)
 $1685万
 $30,694/呎
-(26年-03月)</t>
+(26年-03月-22日)</t>
         </is>
       </c>
     </row>
@@ -39071,7 +39071,7 @@
           <t>A | 669呎 (3房)
 $2028万
 $30,318/呎
-(25年-09月)</t>
+(25年-09月-10日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -39079,7 +39079,7 @@
           <t>B | 579呎 (2房)
 $1722万
 $29,743/呎
-(25年-09月)</t>
+(25年-09月-11日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -39087,7 +39087,7 @@
           <t>C | 569呎 (3房)
 $1725万
 $30,318/呎
-(25年-09月)</t>
+(25年-09月-10日)</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
@@ -39135,7 +39135,7 @@
           <t>J | 549呎 (2房)
 $1676万
 $30,534/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
     </row>
@@ -39150,7 +39150,7 @@
           <t>A | 669呎 (3房)
 $2018万
 $30,167/呎
-(25年-09月)</t>
+(25年-09月-16日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -39158,7 +39158,7 @@
           <t>B | 579呎 (2房)
 $1714万
 $29,594/呎
-(25年-09月)</t>
+(25年-09月-24日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -39166,7 +39166,7 @@
           <t>C | 568呎 (3房)
 $1716万
 $30,220/呎
-(25年-11月)</t>
+(25年-11月-24日)</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
@@ -39214,7 +39214,7 @@
           <t>J | 549呎 (2房)
 $1668万
 $30,383/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
     </row>
@@ -39229,7 +39229,7 @@
           <t>A | 669呎 (3房)
 $2008万
 $30,016/呎
-(25年-09月)</t>
+(25年-09月-10日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -39237,7 +39237,7 @@
           <t>B | 579呎 (2房)
 $1724万
 $29,781/呎
-(25年-09月)</t>
+(25年-09月-15日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -39245,7 +39245,7 @@
           <t>C | 568呎 (3房)
 $1708万
 $30,069/呎
-(26年-01月)</t>
+(26年-01月-18日)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
@@ -39293,7 +39293,7 @@
           <t>J | 549呎 (2房)
 $1681万
 $30,614/呎
-(26年-03月)</t>
+(26年-03月-18日)</t>
         </is>
       </c>
     </row>
@@ -39308,7 +39308,7 @@
           <t>A | 669呎 (3房)
 $1998万
 $29,867/呎
-(25年-10月)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -39316,7 +39316,7 @@
           <t>B | 579呎 (2房)
 $1696万
 $29,299/呎
-(25年-09月)</t>
+(25年-09月-10日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -39324,7 +39324,7 @@
           <t>C | 569呎 (3房)
 $1699万
 $29,866/呎
-(25年-11月)</t>
+(25年-11月-17日)</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr">
@@ -39372,7 +39372,7 @@
           <t>J | 549呎 (2房)
 $1635万
 $29,783/呎
-(26年-03月)</t>
+(26年-03月-17日)</t>
         </is>
       </c>
     </row>
@@ -39387,7 +39387,7 @@
           <t>A | 670呎 (3房)
 $2048万
 $30,564/呎
-(25年-10月)</t>
+(25年-10月-27日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -39395,7 +39395,7 @@
           <t>B | 579呎 (2房)
 $1688万
 $29,152/呎
-(25年-10月)</t>
+(25年-10月-30日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -39403,7 +39403,7 @@
           <t>C | 569呎 (3房)
 $1729万
 $30,392/呎
-(26年-01月)</t>
+(26年-01月-11日)</t>
         </is>
       </c>
       <c r="E26" s="21" t="inlineStr">
@@ -39451,7 +39451,7 @@
           <t>J | 549呎 (2房)
 $1611万
 $29,341/呎
-(26年-03月)</t>
+(26年-03月-19日)</t>
         </is>
       </c>
     </row>
@@ -39466,7 +39466,7 @@
           <t>A | 669呎 (3房)
 $1978万
 $29,568/呎
-(25年-09月)</t>
+(25年-09月-22日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -39474,7 +39474,7 @@
           <t>B | 579呎 (2房)
 $1680万
 $29,007/呎
-(25年-10月)</t>
+(25年-10月-22日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -39482,7 +39482,7 @@
           <t>C | 568呎 (3房)
 $1682万
 $29,620/呎
-(26年-01月)</t>
+(26年-01月-11日)</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr">
@@ -39530,7 +39530,7 @@
           <t>J | 549呎 (2房)
 $1603万
 $29,195/呎
-(26年-02月)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
     </row>
@@ -39545,7 +39545,7 @@
           <t>A | 669呎 (3房)
 $1968万
 $29,420/呎
-(25年-09月)</t>
+(25年-09月-25日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -39553,7 +39553,7 @@
           <t>B | 579呎 (2房)
 $1671万
 $28,862/呎
-(25年-10月)</t>
+(25年-10月-22日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -39561,7 +39561,7 @@
           <t>C | 568呎 (3房)
 $1674万
 $29,472/呎
-(25年-10月)</t>
+(25年-10月-23日)</t>
         </is>
       </c>
       <c r="E28" s="21" t="inlineStr">
@@ -39609,7 +39609,7 @@
           <t>J | 549呎 (2房)
 $1611万
 $29,339/呎
-(26年-03月)</t>
+(26年-03月-22日)</t>
         </is>
       </c>
     </row>
@@ -39624,7 +39624,7 @@
           <t>A | 669呎 (3房)
 $1958万
 $29,269/呎
-(25年-10月)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="C29" s="22" t="inlineStr">
@@ -39632,7 +39632,7 @@
           <t>B | 579呎 (2房)
 $1646万
 $28,428/呎
-(25年-11月)</t>
+(25年-11月-30日)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -39640,7 +39640,7 @@
           <t>C | 568呎 (3房)
 $1649万
 $29,030/呎
-(25年-12月)</t>
+(25年-12月-02日)</t>
         </is>
       </c>
       <c r="E29" s="21" t="inlineStr">
@@ -39688,7 +39688,7 @@
           <t>J | 549呎 (2房)
 $1571万
 $28,612/呎
-(26年-02月)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
     </row>
@@ -39703,7 +39703,7 @@
           <t>A | 670呎 (3房)
 $1941万
 $28,972/呎
-(25年-10月)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="C30" s="22" t="inlineStr">
@@ -39711,7 +39711,7 @@
           <t>B | 579呎 (2房)
 $1630万
 $28,145/呎
-(25年-10月)</t>
+(25年-10月-12日)</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
@@ -39719,7 +39719,7 @@
           <t>C | 568呎 (3房)
 $1632万
 $28,739/呎
-(25年-09月)</t>
+(25年-09月-17日)</t>
         </is>
       </c>
       <c r="E30" s="21" t="inlineStr">
@@ -39767,7 +39767,7 @@
           <t>J | 549呎 (2房)
 $1573万
 $28,648/呎
-(26年-03月)</t>
+(26年-03月-01日)</t>
         </is>
       </c>
     </row>
@@ -39782,7 +39782,7 @@
           <t>A | 670呎 (3房)
 $1902万
 $28,385/呎
-(25年-10月)</t>
+(25年-10月-21日)</t>
         </is>
       </c>
       <c r="C31" s="22" t="inlineStr">
@@ -39790,7 +39790,7 @@
           <t>B | 579呎 (2房)
 $1650万
 $28,496/呎
-(25年-12月)</t>
+(25年-12月-07日)</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -39798,7 +39798,7 @@
           <t>C | 568呎 (3房)
 $1617万
 $28,468/呎
-(25年-12月)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
       <c r="E31" s="21" t="inlineStr">
@@ -39839,7 +39839,7 @@
           <t>J | 549呎 (2房)
 $1555万
 $28,324/呎
-(26年-03月)</t>
+(26年-03月-12日)</t>
         </is>
       </c>
     </row>
@@ -39854,7 +39854,7 @@
           <t>A | 639呎 (2房)
 $1788万
 $27,977/呎
-(25年-11月)</t>
+(25年-11月-04日)</t>
         </is>
       </c>
       <c r="C32" s="24" t="inlineStr"/>
@@ -39883,7 +39883,7 @@
           <t>J | 549呎 (2房)
 $1516万
 $27,623/呎
-(26年-02月)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
     </row>
@@ -39898,7 +39898,7 @@
           <t>A | 639呎 (2房)
 $1761万
 $27,557/呎
-(25年-10月)</t>
+(25年-10月-01日)</t>
         </is>
       </c>
       <c r="C33" s="24" t="inlineStr"/>
@@ -39927,7 +39927,7 @@
           <t>J | 549呎 (2房)
 $1494万
 $27,208/呎
-(26年-03月)</t>
+(26年-03月-01日)</t>
         </is>
       </c>
     </row>
